--- a/ekta-games-import-297.xlsx
+++ b/ekta-games-import-297.xlsx
@@ -992,7 +992,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>8:15 AM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8:15 AM</t>
+          <t>8:30 AM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8:30 AM</t>
+          <t>8:45 AM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8:30 AM</t>
+          <t>8:45 AM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>8:45 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8:45 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>9:15 AM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>9:15 AM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9:15 AM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>9:15 AM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>10:45 AM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>10:45 AM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10:45 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1792,7 +1792,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tt_men_U36-GB-1</t>
+          <t>tt_men_A46-QF3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Under 36 - Group B</t>
+          <t>Above 46 - Quarterfinal</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>U36-GB-1</t>
+          <t>A46-QF3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10:45 AM</t>
+          <t>8:00 AM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Prakshal Shah", "age": 32}</t>
+          <t>{"type": "fixed", "name": "Ghansyam nawani", "age": 60}</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amar Parulekar", "age": 32}</t>
+          <t>{"type": "fixed", "name": "HARSHAPRABHAT SHETTY", "age": 62}</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tt_men_A46-QF3</t>
+          <t>tt_men_U36-GB-1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1857,22 +1857,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Above 46 - Quarterfinal</t>
+          <t>Under 36 - Group B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A46-QF3</t>
+          <t>U36-GB-1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>8:30 AM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ghansyam nawani", "age": 60}</t>
+          <t>{"type": "fixed", "name": "Prakshal Shah", "age": 32}</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "HARSHAPRABHAT SHETTY", "age": 62}</t>
+          <t>{"type": "fixed", "name": "Amar Parulekar", "age": 32}</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -3277,7 +3277,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>tt_men_U36-FINAL</t>
+          <t>tt_men_A46-QF4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Under 36 - Final</t>
+          <t>Above 46 - Quarterfinal</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>U36-FINAL</t>
+          <t>A46-QF4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U36-SF1"}</t>
+          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U36-SF2"}</t>
+          <t>{"type": "fixed", "name": "Sushil Dashpute", "age": 62}</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3332,7 +3332,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>tt_men_A46-QF4</t>
+          <t>tt_men_U36-FINAL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Above 46 - Quarterfinal</t>
+          <t>Under 36 - Final</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>A46-QF4</t>
+          <t>U36-FINAL</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
+          <t>{"type": "placeholder", "ref": "U36-SF1"}</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sushil Dashpute", "age": 62}</t>
+          <t>{"type": "placeholder", "ref": "U36-SF2"}</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3387,7 +3387,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>tt_men_U46-GA-10</t>
+          <t>tt_men_A46-SF2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Under 46 - Group A</t>
+          <t>Above 46 - Semifinal</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>U46-GA-10</t>
+          <t>A46-SF2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
+          <t>{"type": "placeholder", "ref": "A46-QF3"}</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Anuj Shah", "age": 39}</t>
+          <t>{"type": "placeholder", "ref": "A46-QF4"}</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3442,7 +3442,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>tt_men_A46-SF2</t>
+          <t>tt_men_U46-GA-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Above 46 - Semifinal</t>
+          <t>Under 46 - Group A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>A46-SF2</t>
+          <t>U46-GA-10</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-QF3"}</t>
+          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-QF4"}</t>
+          <t>{"type": "fixed", "name": "Anuj Shah", "age": 39}</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>tt_men_U46-GB-7</t>
+          <t>tt_men_A46-R1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Above 46 - Round 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>U46-GB-7</t>
+          <t>A46-R1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4687,12 +4687,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
+          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
+          <t>{"type": "fixed", "name": "Ajit nair", "age": 59}</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4707,7 +4707,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>tt_men_U46-SF1</t>
+          <t>tt_men_U46-GB-7</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4717,22 +4717,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Under 46 - Semifinal</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>U46-SF1</t>
+          <t>U46-GB-7</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>3:15 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 1st"}</t>
+          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 2nd"}</t>
+          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4762,7 +4762,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tt_men_U46-SF2</t>
+          <t>tt_men_A46-QF1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Under 46 - Semifinal</t>
+          <t>Above 46 - Quarterfinal</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>U46-SF2</t>
+          <t>A46-QF1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 1st"}</t>
+          <t>{"type": "placeholder", "ref": "A46-R1"}</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 2nd"}</t>
+          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4817,7 +4817,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>tt_men_U46-FINAL</t>
+          <t>tt_men_U46-SF1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4827,22 +4827,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Under 46 - Final</t>
+          <t>Under 46 - Semifinal</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>U46-FINAL</t>
+          <t>U46-SF1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>3:30 PM</t>
+          <t>3:15 PM</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U46-SF1"}</t>
+          <t>{"type": "manual", "name": "Group B 1st"}</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U46-SF2"}</t>
+          <t>{"type": "manual", "name": "Group A 2nd"}</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4872,7 +4872,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>tt_men_A46-R1</t>
+          <t>tt_men_A46-SF1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Above 46 - Round 1</t>
+          <t>Above 46 - Semifinal</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>A46-R1</t>
+          <t>A46-SF1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>3:45 PM</t>
+          <t>3:30 PM</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
+          <t>{"type": "placeholder", "ref": "A46-QF1"}</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ajit nair", "age": 59}</t>
+          <t>{"type": "placeholder", "ref": "A46-QF2"}</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>tt_men_A46-QF1</t>
+          <t>tt_men_U46-SF2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4937,22 +4937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Above 46 - Quarterfinal</t>
+          <t>Under 46 - Semifinal</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>A46-QF1</t>
+          <t>U46-SF2</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>3:30 PM</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-R1"}</t>
+          <t>{"type": "manual", "name": "Group A 1st"}</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
+          <t>{"type": "manual", "name": "Group B 2nd"}</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4982,7 +4982,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>tt_men_A46-SF1</t>
+          <t>tt_men_A46-FINAL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4992,17 +4992,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Above 46 - Semifinal</t>
+          <t>Above 46 - Final</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>A46-SF1</t>
+          <t>A46-FINAL</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>4:15 PM</t>
+          <t>3:45 PM</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-QF1"}</t>
+          <t>{"type": "placeholder", "ref": "A46-SF1"}</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-QF2"}</t>
+          <t>{"type": "placeholder", "ref": "A46-SF2"}</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5037,7 +5037,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>tt_men_A46-FINAL</t>
+          <t>tt_men_U46-FINAL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5047,22 +5047,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Above 46 - Final</t>
+          <t>Under 46 - Final</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>A46-FINAL</t>
+          <t>U46-FINAL</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>4:30 PM</t>
+          <t>3:45 PM</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-SF1"}</t>
+          <t>{"type": "placeholder", "ref": "U46-SF1"}</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-SF2"}</t>
+          <t>{"type": "placeholder", "ref": "U46-SF2"}</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>3:30 PM</t>
+          <t>4:15 PM</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">

--- a/ekta-games-import-297.xlsx
+++ b/ekta-games-import-297.xlsx
@@ -13177,7 +13177,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>chess_U11-3</t>
+          <t>chess_1220-2</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -13187,17 +13187,17 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Under 11 - Pool</t>
+          <t>12 to 20 - Pool</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>U11-3</t>
+          <t>1220-2</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>8:30 AM</t>
+          <t>8:20 AM</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -13212,12 +13212,12 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rushabh", "age": 8}</t>
+          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Kartik Relan", "age": 9}</t>
+          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -13232,7 +13232,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>chess_U11-4</t>
+          <t>chess_2140-2</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -13242,17 +13242,17 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Under 11 - Pool</t>
+          <t>21 to 40 - Pool</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>U11-4</t>
+          <t>2140-2</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>8:30 AM</t>
+          <t>8:20 AM</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -13267,12 +13267,12 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Neev Chauhan", "age": 8}</t>
+          <t>{"type": "fixed", "name": "Swati Tripathi", "age": 38}</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Jimit Relan", "age": 11}</t>
+          <t>{"type": "fixed", "name": "Amit Nawandhar", "age": 39}</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -13287,7 +13287,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>chess_1220-1</t>
+          <t>chess_U11-3</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -13297,17 +13297,17 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>12 to 20 - Pool</t>
+          <t>Under 11 - Pool</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1220-1</t>
+          <t>U11-3</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>8:50 AM</t>
+          <t>8:40 AM</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
+          <t>{"type": "fixed", "name": "Rushabh", "age": 8}</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Maitreya Manvik", "age": 14}</t>
+          <t>{"type": "fixed", "name": "Kartik Relan", "age": 9}</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -13342,7 +13342,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>chess_U11-5</t>
+          <t>chess_U11-4</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>U11-5</t>
+          <t>U11-4</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>8:40 AM</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Kartik Relan", "age": 9}</t>
+          <t>{"type": "fixed", "name": "Neev Chauhan", "age": 8}</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -13397,7 +13397,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>chess_U11-6</t>
+          <t>chess_1220-1</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -13407,17 +13407,17 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Under 11 - Pool</t>
+          <t>12 to 20 - Pool</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>U11-6</t>
+          <t>1220-1</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>9:10 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rushabh", "age": 8}</t>
+          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Parth yadav", "age": 10}</t>
+          <t>{"type": "fixed", "name": "Maitreya Manvik", "age": 14}</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -13452,7 +13452,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>chess_U11-7</t>
+          <t>chess_2140-6</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -13462,22 +13462,22 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Under 11 - Pool</t>
+          <t>21 to 40 - Pool</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>U11-7</t>
+          <t>2140-6</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -13487,12 +13487,12 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rushabh", "age": 8}</t>
+          <t>{"type": "fixed", "name": "Tej", "age": 32}</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Jimit Relan", "age": 11}</t>
+          <t>{"type": "fixed", "name": "Swati Tripathi", "age": 38}</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -13507,7 +13507,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>chess_U11-8</t>
+          <t>chess_U11-5</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -13522,17 +13522,17 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>U11-8</t>
+          <t>U11-5</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>9:20 AM</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -13542,12 +13542,12 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Neev Chauhan", "age": 8}</t>
+          <t>{"type": "fixed", "name": "Kartik Relan", "age": 9}</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Kartik Relan", "age": 9}</t>
+          <t>{"type": "fixed", "name": "Jimit Relan", "age": 11}</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -13562,7 +13562,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>chess_1220-2</t>
+          <t>chess_U11-6</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -13572,22 +13572,22 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>12 to 20 - Pool</t>
+          <t>Under 11 - Pool</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1220-2</t>
+          <t>U11-6</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>10:50 AM</t>
+          <t>9:20 AM</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -13597,12 +13597,12 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
+          <t>{"type": "fixed", "name": "Rushabh", "age": 8}</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
+          <t>{"type": "fixed", "name": "Parth yadav", "age": 10}</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -13617,7 +13617,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>chess_U11-9</t>
+          <t>chess_U11-7</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -13632,17 +13632,17 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>U11-9</t>
+          <t>U11-7</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -13652,12 +13652,12 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Neev Chauhan", "age": 8}</t>
+          <t>{"type": "fixed", "name": "Rushabh", "age": 8}</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Parth yadav", "age": 10}</t>
+          <t>{"type": "fixed", "name": "Jimit Relan", "age": 11}</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -13672,7 +13672,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>chess_1220-3</t>
+          <t>chess_U11-8</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -13682,22 +13682,22 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>12 to 20 - Pool</t>
+          <t>Under 11 - Pool</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>1220-3</t>
+          <t>U11-8</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>11:20 AM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -13707,12 +13707,12 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
+          <t>{"type": "fixed", "name": "Neev Chauhan", "age": 8}</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
+          <t>{"type": "fixed", "name": "Kartik Relan", "age": 9}</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -13727,7 +13727,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>chess_U11-10</t>
+          <t>chess_1220-3</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -13737,22 +13737,22 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Under 11 - Pool</t>
+          <t>12 to 20 - Pool</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>U11-10</t>
+          <t>1220-3</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>11:30 AM</t>
+          <t>10:50 AM</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Parth yadav", "age": 10}</t>
+          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Jimit Relan", "age": 11}</t>
+          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>11:50 AM</t>
+          <t>10:50 AM</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -13837,7 +13837,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>chess_1220-5</t>
+          <t>chess_2140-3</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -13847,22 +13847,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>12 to 20 - Pool</t>
+          <t>21 to 40 - Pool</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>1220-5</t>
+          <t>2140-3</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>11:10 AM</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -13872,12 +13872,12 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
+          <t>{"type": "fixed", "name": "Amit Nawandhar", "age": 39}</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -13892,7 +13892,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>chess_1220-6</t>
+          <t>chess_U11-9</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -13902,22 +13902,22 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>12 to 20 - Pool</t>
+          <t>Under 11 - Pool</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>1220-6</t>
+          <t>U11-9</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>11:10 AM</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -13927,12 +13927,12 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Maitreya Manvik", "age": 14}</t>
+          <t>{"type": "fixed", "name": "Neev Chauhan", "age": 8}</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
+          <t>{"type": "fixed", "name": "Parth yadav", "age": 10}</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -13947,7 +13947,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>chess_2140-1</t>
+          <t>chess_1220-5</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -13957,17 +13957,17 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>21 to 40 - Pool</t>
+          <t>12 to 20 - Pool</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2140-1</t>
+          <t>1220-5</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>3:20 PM</t>
+          <t>11:30 AM</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -13982,12 +13982,12 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tej", "age": 32}</t>
+          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tejas doshi", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -14002,7 +14002,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>chess_2140-2</t>
+          <t>chess_1220-6</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -14012,17 +14012,17 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>21 to 40 - Pool</t>
+          <t>12 to 20 - Pool</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2140-2</t>
+          <t>1220-6</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>3:20 PM</t>
+          <t>11:30 AM</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -14037,12 +14037,12 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Swati Tripathi", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Maitreya Manvik", "age": 14}</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amit Nawandhar", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -14057,7 +14057,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>chess_2140-3</t>
+          <t>chess_2140-1</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -14072,17 +14072,17 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2140-3</t>
+          <t>2140-1</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>3:50 PM</t>
+          <t>11:50 AM</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -14092,12 +14092,12 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Tej", "age": 32}</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amit Nawandhar", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Tejas doshi", "age": 40}</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -14112,7 +14112,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>chess_2140-4</t>
+          <t>chess_U11-10</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -14122,22 +14122,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>21 to 40 - Pool</t>
+          <t>Under 11 - Pool</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2140-4</t>
+          <t>U11-10</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>3:50 PM</t>
+          <t>11:50 AM</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -14147,12 +14147,12 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Swati Tripathi", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Parth yadav", "age": 10}</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tejas doshi", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Jimit Relan", "age": 11}</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -14167,7 +14167,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>chess_2140-5</t>
+          <t>chess_2140-4</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -14182,17 +14182,17 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2140-5</t>
+          <t>2140-4</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>4:20 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -14202,7 +14202,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amit Nawandhar", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Swati Tripathi", "age": 38}</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -14222,7 +14222,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>chess_2140-6</t>
+          <t>chess_41P-1</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -14232,17 +14232,17 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>21 to 40 - Pool</t>
+          <t>41 and above - Pool</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2140-6</t>
+          <t>41P-1</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>4:45 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -14257,12 +14257,12 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tej", "age": 32}</t>
+          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Swati Tripathi", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Ajit nair", "age": 59}</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -14277,7 +14277,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>chess_2140-7</t>
+          <t>chess_2140-10</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -14292,12 +14292,12 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2140-7</t>
+          <t>2140-10</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>5:10 PM</t>
+          <t>3:20 PM</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Amit Nawandhar", "age": 39}</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -14332,7 +14332,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>chess_2140-8</t>
+          <t>chess_41P-8</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -14342,22 +14342,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>21 to 40 - Pool</t>
+          <t>41 and above - Pool</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2140-8</t>
+          <t>41P-8</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>5:40 PM</t>
+          <t>3:20 PM</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tejas doshi", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>5:40 PM</t>
+          <t>3:40 PM</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -14442,7 +14442,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>chess_41P-1</t>
+          <t>chess_41P-12</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>41P-1</t>
+          <t>41P-12</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>3:40 PM</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
+          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -14497,7 +14497,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>chess_2140-10</t>
+          <t>chess_2140-5</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2140-10</t>
+          <t>2140-5</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>6:10 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Tejas doshi", "age": 40}</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
@@ -14552,7 +14552,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>chess_2140-11</t>
+          <t>chess_41P-3</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -14562,22 +14562,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>21 to 40 - Pool</t>
+          <t>41 and above - Pool</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2140-11</t>
+          <t>41P-3</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>6:40 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -14587,12 +14587,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Swati Tripathi", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -14607,7 +14607,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>chess_2140-12</t>
+          <t>chess_2140-13</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -14622,12 +14622,12 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2140-12</t>
+          <t>2140-13</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>4:20 PM</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -14642,12 +14642,12 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tej", "age": 32}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amit Nawandhar", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Swati Tripathi", "age": 38}</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -14662,7 +14662,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>chess_2140-13</t>
+          <t>chess_41P-2</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -14672,17 +14672,17 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>21 to 40 - Pool</t>
+          <t>41 and above - Pool</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2140-13</t>
+          <t>41P-2</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>4:20 PM</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -14697,12 +14697,12 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Ajit nair", "age": 59}</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Swati Tripathi", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
@@ -14717,7 +14717,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>chess_2140-14</t>
+          <t>chess_2140-12</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -14732,12 +14732,12 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2140-14</t>
+          <t>2140-12</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>4:40 PM</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Amit Nawandhar", "age": 39}</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
@@ -14772,7 +14772,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>chess_41P-2</t>
+          <t>chess_41P-6</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -14787,12 +14787,12 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>41P-2</t>
+          <t>41P-6</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>4:40 PM</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -14807,12 +14807,12 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ajit nair", "age": 59}</t>
+          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
+          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -14827,7 +14827,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>chess_41P-3</t>
+          <t>chess_2140-15</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -14837,17 +14837,17 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>41 and above - Pool</t>
+          <t>21 to 40 - Pool</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>41P-3</t>
+          <t>2140-15</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>7:50 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -14862,12 +14862,12 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
+          <t>{"type": "fixed", "name": "Tejas doshi", "age": 40}</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -14882,7 +14882,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>chess_41P-4</t>
+          <t>chess_41P-11</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -14897,17 +14897,17 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>41P-4</t>
+          <t>41P-11</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>8:20 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
+          <t>{"type": "fixed", "name": "Sachin Malgadnkar", "age": 52}</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -14937,7 +14937,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>chess_41P-5</t>
+          <t>chess_2140-11</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -14947,22 +14947,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>41 and above - Pool</t>
+          <t>21 to 40 - Pool</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>41P-5</t>
+          <t>2140-11</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>8:20 PM</t>
+          <t>5:20 PM</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
+          <t>{"type": "fixed", "name": "Swati Tripathi", "age": 38}</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ajit nair", "age": 59}</t>
+          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -14992,7 +14992,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>chess_2140-15</t>
+          <t>chess_41P-16</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -15002,22 +15002,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>21 to 40 - Pool</t>
+          <t>41 and above - Pool</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2140-15</t>
+          <t>41P-16</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>8:40 PM</t>
+          <t>5:20 PM</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tejas doshi", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Harkishin malkan", "age": 76}</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -15047,7 +15047,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>chess_41P-6</t>
+          <t>chess_1220-FINAL</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -15057,17 +15057,17 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>41 and above - Pool</t>
+          <t>12 to 20 - Final</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>41P-6</t>
+          <t>1220-FINAL</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>8:55 PM</t>
+          <t>5:40 PM</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -15082,12 +15082,12 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
+          <t>{"type": "manual", "name": "Pool 1st"}</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
+          <t>{"type": "manual", "name": "Pool 2nd"}</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -15102,7 +15102,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>chess_41P-7</t>
+          <t>chess_41P-17</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -15117,17 +15117,17 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>41P-7</t>
+          <t>41P-17</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>9:25 PM</t>
+          <t>5:40 PM</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -15137,12 +15137,12 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
+          <t>{"type": "fixed", "name": "Sachin Malgadnkar", "age": 52}</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sachin Malgadnkar", "age": 52}</t>
+          <t>{"type": "fixed", "name": "Ajit nair", "age": 59}</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -15157,7 +15157,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>chess_41P-8</t>
+          <t>chess_2140-7</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -15167,22 +15167,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>41 and above - Pool</t>
+          <t>21 to 40 - Pool</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>41P-8</t>
+          <t>2140-7</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>9:45 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -15192,12 +15192,12 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
+          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
@@ -15212,7 +15212,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>chess_41P-9</t>
+          <t>chess_41P-18</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -15227,12 +15227,12 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>41P-9</t>
+          <t>41P-18</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>8:15 AM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -15242,17 +15242,17 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
+          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
+          <t>{"type": "fixed", "name": "Harkishin malkan", "age": 76}</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -15267,7 +15267,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>chess_41P-10</t>
+          <t>chess_U11-FINAL</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -15277,17 +15277,17 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>41 and above - Pool</t>
+          <t>Under 11 - Final</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>41P-10</t>
+          <t>U11-FINAL</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>8:45 AM</t>
+          <t>6:20 PM</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -15297,17 +15297,17 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
+          <t>{"type": "manual", "name": "Pool 1st"}</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
+          <t>{"type": "manual", "name": "Pool 2nd"}</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -15322,7 +15322,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>chess_41P-11</t>
+          <t>chess_2140-14</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -15332,17 +15332,17 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>41 and above - Pool</t>
+          <t>21 to 40 - Pool</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>41P-11</t>
+          <t>2140-14</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>8:45 AM</t>
+          <t>6:30 PM</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -15352,17 +15352,17 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sachin Malgadnkar", "age": 52}</t>
+          <t>{"type": "fixed", "name": "Tej", "age": 32}</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
+          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -15377,7 +15377,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>chess_41P-12</t>
+          <t>chess_41P-7</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -15392,12 +15392,12 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>41P-12</t>
+          <t>41P-7</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>9:15 AM</t>
+          <t>6:40 PM</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -15407,17 +15407,17 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
+          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ajit nair", "age": 59}</t>
+          <t>{"type": "fixed", "name": "Sachin Malgadnkar", "age": 52}</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -15432,7 +15432,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>chess_41P-13</t>
+          <t>chess_41P-20</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -15447,12 +15447,12 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>41P-13</t>
+          <t>41P-20</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>9:15 AM</t>
+          <t>6:50 PM</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -15462,17 +15462,17 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sachin Malgadnkar", "age": 52}</t>
+          <t>{"type": "fixed", "name": "Ajit nair", "age": 59}</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
+          <t>{"type": "fixed", "name": "Harkishin malkan", "age": 76}</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -15487,7 +15487,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>chess_41P-14</t>
+          <t>chess_2140-8</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -15497,37 +15497,37 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>41 and above - Pool</t>
+          <t>21 to 40 - Pool</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>41P-14</t>
+          <t>2140-8</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>9:35 AM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
+          <t>{"type": "fixed", "name": "Tejas doshi", "age": 40}</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Harkishin malkan", "age": 76}</t>
+          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -15542,7 +15542,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>chess_41P-15</t>
+          <t>chess_41P-10</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -15557,22 +15557,22 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>41P-15</t>
+          <t>41P-10</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>9:45 AM</t>
+          <t>7:10 PM</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sachin Malgadnkar", "age": 52}</t>
+          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
@@ -15597,7 +15597,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>chess_41P-16</t>
+          <t>chess_41P-14</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -15612,12 +15612,12 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>41P-16</t>
+          <t>41P-14</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>10:15 AM</t>
+          <t>7:20 PM</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
+          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -15652,7 +15652,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>chess_41P-17</t>
+          <t>chess_2140-FINAL</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -15662,17 +15662,17 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>41 and above - Pool</t>
+          <t>21 to 40 - Final</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>41P-17</t>
+          <t>2140-FINAL</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>10:15 AM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -15682,17 +15682,17 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sachin Malgadnkar", "age": 52}</t>
+          <t>{"type": "manual", "name": "Pool 1st"}</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ajit nair", "age": 59}</t>
+          <t>{"type": "manual", "name": "Pool 2nd"}</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
@@ -15707,7 +15707,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>chess_41P-18</t>
+          <t>chess_41P-5</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -15722,12 +15722,12 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>41P-18</t>
+          <t>41P-5</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>10:45 AM</t>
+          <t>7:40 PM</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -15737,17 +15737,17 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
+          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Harkishin malkan", "age": 76}</t>
+          <t>{"type": "fixed", "name": "Ajit nair", "age": 59}</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
@@ -15762,7 +15762,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>chess_41P-19</t>
+          <t>chess_41P-21</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -15777,27 +15777,27 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>41P-19</t>
+          <t>41P-21</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>11:15 AM</t>
+          <t>7:50 PM</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
+          <t>{"type": "fixed", "name": "Sachin Malgadnkar", "age": 52}</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -15817,7 +15817,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>chess_41P-20</t>
+          <t>chess_41P-4</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -15832,12 +15832,12 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>41P-20</t>
+          <t>41P-4</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>11:45 AM</t>
+          <t>8:10 PM</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -15847,17 +15847,17 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ajit nair", "age": 59}</t>
+          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Harkishin malkan", "age": 76}</t>
+          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -15872,7 +15872,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>chess_41P-21</t>
+          <t>chess_41P-13</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -15887,22 +15887,22 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>41P-21</t>
+          <t>41P-13</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>8:20 PM</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -15912,7 +15912,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Harkishin malkan", "age": 76}</t>
+          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -15927,7 +15927,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>chess_1220-FINAL</t>
+          <t>chess_41P-15</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -15937,17 +15937,17 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>12 to 20 - Final</t>
+          <t>41 and above - Pool</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>1220-FINAL</t>
+          <t>41P-15</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>3:20 PM</t>
+          <t>8:55 PM</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -15957,17 +15957,17 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Pool 1st"}</t>
+          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Pool 2nd"}</t>
+          <t>{"type": "fixed", "name": "Sachin Malgadnkar", "age": 52}</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -15982,7 +15982,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>chess_U11-FINAL</t>
+          <t>chess_41P-19</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -15992,17 +15992,17 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Under 11 - Final</t>
+          <t>41 and above - Pool</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>U11-FINAL</t>
+          <t>41P-19</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>3:20 PM</t>
+          <t>9:35 PM</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -16012,17 +16012,17 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Pool 1st"}</t>
+          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Pool 2nd"}</t>
+          <t>{"type": "fixed", "name": "Harkishin malkan", "age": 76}</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -16037,7 +16037,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>chess_2140-FINAL</t>
+          <t>chess_41P-9</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -16047,17 +16047,17 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>21 to 40 - Final</t>
+          <t>41 and above - Pool</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2140-FINAL</t>
+          <t>41P-9</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>3:40 PM</t>
+          <t>9:35 PM</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -16067,17 +16067,17 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Pool 1st"}</t>
+          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Pool 2nd"}</t>
+          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -16112,7 +16112,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>9:55 PM</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -16122,7 +16122,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -16167,17 +16167,17 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>4:20 PM</t>
+          <t>9:55 PM</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -16222,7 +16222,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>4:40 PM</t>
+          <t>8:00 AM</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">

--- a/ekta-games-import-297.xlsx
+++ b/ekta-games-import-297.xlsx
@@ -5532,7 +5532,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GA-2</t>
+          <t>carrom_men_CM-U46-GB-1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5542,22 +5542,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Under 46 - Group A</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>CM-U46-GA-2</t>
+          <t>CM-U46-GB-1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>8:25 AM</t>
+          <t>8:15 AM</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Anuj Shah", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5587,7 +5587,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GA-3</t>
+          <t>carrom_men_CM-U46-GB-2</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5597,22 +5597,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Under 46 - Group A</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CM-U46-GA-3</t>
+          <t>CM-U46-GB-2</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>8:40 AM</t>
+          <t>8:15 AM</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Abhishek Dugar", "age": 34}</t>
+          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
+          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5642,7 +5642,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GA-4</t>
+          <t>carrom_men_CM-U46-GB-3</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5652,17 +5652,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Under 46 - Group A</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>CM-U46-GA-4</t>
+          <t>CM-U46-GB-3</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>9:05 AM</t>
+          <t>8:15 AM</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Amar Jain", "age": 42}</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
+          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5697,7 +5697,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GA-5</t>
+          <t>carrom_men_CM-U46-GA-3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CM-U46-GA-5</t>
+          <t>CM-U46-GA-3</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>9:20 AM</t>
+          <t>8:30 AM</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Anuj Shah", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -5752,7 +5752,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GB-1</t>
+          <t>carrom_men_CM-U15-1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5762,17 +5762,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Under 15 - Pool</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CM-U46-GB-1</t>
+          <t>CM-U15-1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>8:45 AM</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Aarav Pilankar", "age": 11}</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Yash agarwal", "age": 13}</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -5807,7 +5807,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GA-6</t>
+          <t>carrom_men_CM-U46-GB-4</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5817,22 +5817,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Under 46 - Group A</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>CM-U46-GA-6</t>
+          <t>CM-U46-GB-4</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>10:45 AM</t>
+          <t>8:45 AM</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
+          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Anuj Shah", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -5862,7 +5862,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GB-2</t>
+          <t>carrom_men_CM-U46-GB-5</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>CM-U46-GB-2</t>
+          <t>CM-U46-GB-5</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>10:45 AM</t>
+          <t>8:45 AM</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
+          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5917,7 +5917,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GA-7</t>
+          <t>carrom_men_CM-U46-GA-2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5932,17 +5932,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>CM-U46-GA-7</t>
+          <t>CM-U46-GA-2</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
+          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Abhishek Dugar", "age": 34}</t>
+          <t>{"type": "fixed", "name": "Anuj Shah", "age": 39}</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5972,7 +5972,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GB-3</t>
+          <t>carrom_men_CM-U46-GA-7</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5982,17 +5982,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Under 46 - Group A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>CM-U46-GB-3</t>
+          <t>CM-U46-GA-7</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>11:15 AM</t>
+          <t>9:15 AM</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amar Jain", "age": 42}</t>
+          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Abhishek Dugar", "age": 34}</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -6027,7 +6027,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GA-8</t>
+          <t>carrom_men_CM-U46-GB-6</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6037,17 +6037,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Under 46 - Group A</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>CM-U46-GA-8</t>
+          <t>CM-U46-GB-6</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>11:25 AM</t>
+          <t>9:15 AM</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -6062,12 +6062,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
+          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Amar Jain", "age": 42}</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -6082,7 +6082,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GB-4</t>
+          <t>carrom_men_CM-U46-GB-7</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6097,17 +6097,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>CM-U46-GB-4</t>
+          <t>CM-U46-GB-7</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>11:30 AM</t>
+          <t>9:15 AM</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6137,7 +6137,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GA-10</t>
+          <t>carrom_men_CM-U46-GA-4</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6152,12 +6152,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CM-U46-GA-10</t>
+          <t>CM-U46-GA-4</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>11:50 AM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
+          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6192,7 +6192,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GA-9</t>
+          <t>carrom_men_CM-U15-2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6202,22 +6202,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Under 46 - Group A</t>
+          <t>Under 15 - Pool</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>CM-U46-GA-9</t>
+          <t>CM-U15-2</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>11:50 AM</t>
+          <t>10:45 AM</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Abhishek Dugar", "age": 34}</t>
+          <t>{"type": "fixed", "name": "Shaurya Tripathi", "age": 10}</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Aarav Pilankar", "age": 11}</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6247,7 +6247,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GA-11</t>
+          <t>carrom_men_CM-U46-GA-5</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6262,17 +6262,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>CM-U46-GA-11</t>
+          <t>CM-U46-GA-5</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>10:45 AM</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Abhishek Dugar", "age": 34}</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Anuj Shah", "age": 39}</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -6302,7 +6302,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GA-12</t>
+          <t>carrom_men_CM-U46-GA-8</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>CM-U46-GA-12</t>
+          <t>CM-U46-GA-8</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>10:45 AM</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6342,7 +6342,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Anuj Shah", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6357,7 +6357,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GB-5</t>
+          <t>carrom_men_CM-U46-GB-8</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>CM-U46-GB-5</t>
+          <t>CM-U46-GB-8</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>3:15 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6412,7 +6412,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GA-13</t>
+          <t>carrom_men_CM-U46-GA-12</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6427,17 +6427,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>CM-U46-GA-13</t>
+          <t>CM-U46-GA-12</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>3:25 PM</t>
+          <t>11:15 AM</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
+          <t>{"type": "fixed", "name": "Anuj Shah", "age": 39}</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6467,7 +6467,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GA-14</t>
+          <t>carrom_men_CM-U46-GA-9</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>CM-U46-GA-14</t>
+          <t>CM-U46-GA-9</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>3:25 PM</t>
+          <t>11:15 AM</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Abhishek Dugar", "age": 34}</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Abhishek Dugar", "age": 34}</t>
+          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -6522,7 +6522,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U15-1</t>
+          <t>carrom_men_CM-U15-3</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6537,17 +6537,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>CM-U15-1</t>
+          <t>CM-U15-3</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>3:40 PM</t>
+          <t>11:30 AM</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aarav Pilankar", "age": 11}</t>
+          <t>{"type": "fixed", "name": "Shaurya Tripathi", "age": 10}</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6577,7 +6577,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GB-6</t>
+          <t>carrom_men_CM-U46-GB-12</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>CM-U46-GB-6</t>
+          <t>CM-U46-GB-12</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>3:40 PM</t>
+          <t>11:30 AM</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
+          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
           <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>{"type": "fixed", "name": "Amar Jain", "age": 42}</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -6632,7 +6632,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GB-7</t>
+          <t>carrom_men_CM-U46-GB-9</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6647,17 +6647,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>CM-U46-GB-7</t>
+          <t>CM-U46-GB-9</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>3:40 PM</t>
+          <t>11:30 AM</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6667,12 +6667,12 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Amar Jain", "age": 42}</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
+          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -6687,7 +6687,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U15-2</t>
+          <t>carrom_men_CM-A46-GA-1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6697,22 +6697,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Under 15 - Pool</t>
+          <t>Above 46 - Group A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>CM-U15-2</t>
+          <t>CM-A46-GA-1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>4:05 PM</t>
+          <t>11:45 AM</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Shaurya Tripathi", "age": 10}</t>
+          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aarav Pilankar", "age": 11}</t>
+          <t>{"type": "fixed", "name": "Mr. Hiral Khadepau", "age": 52}</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6742,7 +6742,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GB-8</t>
+          <t>carrom_men_CM-A46-GB-1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6752,22 +6752,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Above 46 - Group B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>CM-U46-GB-8</t>
+          <t>CM-A46-GB-1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4:05 PM</t>
+          <t>11:45 AM</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Vinod Agrawal", "age": 55}</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6797,7 +6797,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GB-9</t>
+          <t>carrom_men_CM-U46-GA-10</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6807,22 +6807,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Under 46 - Group A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>CM-U46-GB-9</t>
+          <t>CM-U46-GA-10</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>4:05 PM</t>
+          <t>11:45 AM</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amar Jain", "age": 42}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -6852,7 +6852,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GB-10</t>
+          <t>carrom_men_CM-U46-GA-11</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -6862,22 +6862,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Under 46 - Group A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>CM-U46-GB-10</t>
+          <t>CM-U46-GA-11</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4:30 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -6907,7 +6907,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GB-11</t>
+          <t>carrom_men_CM-U46-GA-6</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6917,22 +6917,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Under 46 - Group A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>CM-U46-GB-11</t>
+          <t>CM-U46-GA-6</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4:30 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amar Jain", "age": 42}</t>
+          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
+          <t>{"type": "fixed", "name": "Anuj Shah", "age": 39}</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6962,7 +6962,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GB-12</t>
+          <t>carrom_men_CM-U46-GB-10</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -6977,12 +6977,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>CM-U46-GB-12</t>
+          <t>CM-U46-GB-10</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>4:30 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -7017,7 +7017,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U15-3</t>
+          <t>carrom_men_CM-A46-GA-2</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7027,22 +7027,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Under 15 - Pool</t>
+          <t>Above 46 - Group A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CM-U15-3</t>
+          <t>CM-A46-GA-2</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>4:45 PM</t>
+          <t>3:15 PM</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7052,12 +7052,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Shaurya Tripathi", "age": 10}</t>
+          <t>{"type": "fixed", "name": "Vinay Sawant", "age": 49}</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Yash agarwal", "age": 13}</t>
+          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -7072,7 +7072,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GB-13</t>
+          <t>carrom_men_CM-A46-GB-4</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7082,22 +7082,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Above 46 - Group B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>CM-U46-GB-13</t>
+          <t>CM-A46-GB-4</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>4:55 PM</t>
+          <t>3:15 PM</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -7107,12 +7107,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Vinod Agrawal", "age": 55}</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
+          <t>{"type": "fixed", "name": "Gopal Krishna", "age": 65}</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7127,7 +7127,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GB-14</t>
+          <t>carrom_men_CM-U46-GB-11</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7142,17 +7142,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>CM-U46-GB-14</t>
+          <t>CM-U46-GB-11</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>4:55 PM</t>
+          <t>3:15 PM</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Amar Jain", "age": 42}</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amar Jain", "age": 42}</t>
+          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -7182,7 +7182,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>carrom_men_CM-A46-GA-1</t>
+          <t>carrom_men_U15-FINAL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7192,17 +7192,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Above 46 - Group A</t>
+          <t>Under 15 - Final</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>CM-A46-GA-1</t>
+          <t>U15-FINAL</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>3:30 PM</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
+          <t>{"type": "manual", "name": "Pool 1st"}</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mr. Hiral Khadepau", "age": 52}</t>
+          <t>{"type": "manual", "name": "Pool 2nd"}</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -7237,7 +7237,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>carrom_men_CM-A46-GB-1</t>
+          <t>carrom_men_CM-U46-GA-15</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7247,22 +7247,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Above 46 - Group B</t>
+          <t>Under 46 - Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>CM-A46-GB-1</t>
+          <t>CM-U46-GA-15</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>5:10 PM</t>
+          <t>3:35 PM</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinod Agrawal", "age": 55}</t>
+          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
+          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -7292,7 +7292,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GA-15</t>
+          <t>carrom_men_CM-U46-GB-13</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7302,22 +7302,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Under 46 - Group A</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>CM-U46-GA-15</t>
+          <t>CM-U46-GB-13</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>5:15 PM</t>
+          <t>3:40 PM</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7327,12 +7327,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
+          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7347,7 +7347,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>carrom_men_CM-U46-GB-15</t>
+          <t>carrom_men_CM-A46-GB-2</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7357,22 +7357,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Above 46 - Group B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>CM-U46-GB-15</t>
+          <t>CM-A46-GB-2</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>5:20 PM</t>
+          <t>3:45 PM</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Gopal Krishna", "age": 65}</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7402,7 +7402,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>carrom_men_CM-A46-GB-2</t>
+          <t>carrom_men_CM-U46-GB-14</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7412,17 +7412,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Above 46 - Group B</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>CM-A46-GB-2</t>
+          <t>CM-U46-GB-14</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>5:35 PM</t>
+          <t>3:50 PM</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
+          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Gopal Krishna", "age": 65}</t>
+          <t>{"type": "fixed", "name": "Amar Jain", "age": 42}</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -7457,7 +7457,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>carrom_men_CM-A46-GA-2</t>
+          <t>carrom_men_CM-A46-GA-3</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7472,12 +7472,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>CM-A46-GA-2</t>
+          <t>CM-A46-GA-3</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>5:45 PM</t>
+          <t>3:55 PM</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinay Sawant", "age": 49}</t>
+          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
+          <t>{"type": "fixed", "name": "Mr. Hiral Khadepau", "age": 52}</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -7512,7 +7512,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>carrom_men_CM-A46-GB-3</t>
+          <t>carrom_men_CM-U46-GA-14</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7522,22 +7522,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Above 46 - Group B</t>
+          <t>Under 46 - Group A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>CM-A46-GB-3</t>
+          <t>CM-U46-GA-14</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7547,12 +7547,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinod Agrawal", "age": 55}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
+          <t>{"type": "fixed", "name": "Abhishek Dugar", "age": 34}</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7567,7 +7567,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>carrom_men_CM-A46-GA-3</t>
+          <t>carrom_men_CM-A46-GB-3</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7577,22 +7577,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Above 46 - Group A</t>
+          <t>Above 46 - Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>CM-A46-GA-3</t>
+          <t>CM-A46-GB-3</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>6:10 PM</t>
+          <t>4:05 PM</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
+          <t>{"type": "fixed", "name": "Vinod Agrawal", "age": 55}</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mr. Hiral Khadepau", "age": 52}</t>
+          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -7622,7 +7622,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>carrom_men_CM-A46-GB-4</t>
+          <t>carrom_men_CM-U46-GB-15</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7632,22 +7632,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Above 46 - Group B</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>CM-A46-GB-4</t>
+          <t>CM-U46-GB-15</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>6:25 PM</t>
+          <t>4:10 PM</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7657,12 +7657,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinod Agrawal", "age": 55}</t>
+          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Gopal Krishna", "age": 65}</t>
+          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>6:45 PM</t>
+          <t>4:15 PM</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>6:50 PM</t>
+          <t>4:20 PM</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -7787,7 +7787,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>carrom_men_CM-A46-GA-5</t>
+          <t>carrom_men_CM-U46-GA-13</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -7797,22 +7797,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Above 46 - Group A</t>
+          <t>Under 46 - Group A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>CM-A46-GA-5</t>
+          <t>CM-U46-GA-13</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>7:10 PM</t>
+          <t>4:30 PM</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinay Sawant", "age": 49}</t>
+          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mr. Hiral Khadepau", "age": 52}</t>
+          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7842,7 +7842,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>carrom_men_CM-A46-GA-6</t>
+          <t>carrom_men_CM-A46-GB-6</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7852,22 +7852,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Above 46 - Group A</t>
+          <t>Above 46 - Group B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>CM-A46-GA-6</t>
+          <t>CM-A46-GB-6</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>8:40 PM</t>
+          <t>4:45 PM</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
+          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
+          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -7897,7 +7897,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>carrom_men_CM-A46-GB-6</t>
+          <t>carrom_men_U46-SF1</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7907,17 +7907,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Above 46 - Group B</t>
+          <t>Under 46 - Semifinal</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>CM-A46-GB-6</t>
+          <t>U46-SF1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>9:20 PM</t>
+          <t>4:45 PM</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
+          <t>{"type": "manual", "name": "Group A 1st"}</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
+          <t>{"type": "manual", "name": "Group B 2nd"}</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -7952,7 +7952,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>carrom_men_A46-SF1</t>
+          <t>carrom_men_U46-SF2</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7962,37 +7962,37 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Above 46 - Semifinal</t>
+          <t>Under 46 - Semifinal</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>A46-SF1</t>
+          <t>U46-SF2</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>3:20 PM</t>
+          <t>4:45 PM</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 1st"}</t>
+          <t>{"type": "manual", "name": "Group B 1st"}</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 2nd"}</t>
+          <t>{"type": "manual", "name": "Group A 2nd"}</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -8007,7 +8007,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>carrom_men_U15-FINAL</t>
+          <t>carrom_men_CM-A46-GA-5</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8017,37 +8017,37 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Under 15 - Final</t>
+          <t>Above 46 - Group A</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>U15-FINAL</t>
+          <t>CM-A46-GA-5</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>3:20 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Pool 1st"}</t>
+          <t>{"type": "fixed", "name": "Vinay Sawant", "age": 49}</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Pool 2nd"}</t>
+          <t>{"type": "fixed", "name": "Mr. Hiral Khadepau", "age": 52}</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8062,7 +8062,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>carrom_men_A46-SF2</t>
+          <t>carrom_men_CM-A46-GA-6</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8072,37 +8072,37 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Above 46 - Semifinal</t>
+          <t>Above 46 - Group A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>A46-SF2</t>
+          <t>CM-A46-GA-6</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>3:35 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 1st"}</t>
+          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 2nd"}</t>
+          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8117,7 +8117,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>carrom_men_U46-SF1</t>
+          <t>carrom_men_U46-FINAL</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8127,37 +8127,37 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Under 46 - Semifinal</t>
+          <t>Under 46 - Final</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>U46-SF1</t>
+          <t>U46-FINAL</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>3:35 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 1st"}</t>
+          <t>{"type": "placeholder", "ref": "U46-SF1"}</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 2nd"}</t>
+          <t>{"type": "placeholder", "ref": "U46-SF2"}</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -8172,7 +8172,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>carrom_men_U46-SF2</t>
+          <t>carrom_men_A46-SF1</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8182,37 +8182,37 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Under 46 - Semifinal</t>
+          <t>Above 46 - Semifinal</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>U46-SF2</t>
+          <t>A46-SF1</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>3:35 PM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 1st"}</t>
+          <t>{"type": "manual", "name": "Group A 1st"}</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 2nd"}</t>
+          <t>{"type": "manual", "name": "Group B 2nd"}</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8227,7 +8227,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>carrom_men_A46-FINAL</t>
+          <t>carrom_men_A46-SF2</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8237,37 +8237,37 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Above 46 - Final</t>
+          <t>Above 46 - Semifinal</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>A46-FINAL</t>
+          <t>A46-SF2</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>3:50 PM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-SF1"}</t>
+          <t>{"type": "manual", "name": "Group B 1st"}</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-SF2"}</t>
+          <t>{"type": "manual", "name": "Group A 2nd"}</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8282,7 +8282,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>carrom_men_U46-FINAL</t>
+          <t>carrom_men_A46-FINAL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8292,37 +8292,37 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Under 46 - Final</t>
+          <t>Above 46 - Final</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>U46-FINAL</t>
+          <t>A46-FINAL</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>3:50 PM</t>
+          <t>5:30 PM</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U46-SF1"}</t>
+          <t>{"type": "placeholder", "ref": "A46-SF1"}</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U46-SF2"}</t>
+          <t>{"type": "placeholder", "ref": "A46-SF2"}</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>8:25 AM</t>
+          <t>8:30 AM</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>8:25 AM</t>
+          <t>8:30 AM</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>8:50 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>8:50 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -8687,7 +8687,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>9:15 AM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>9:15 AM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -8797,12 +8797,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -8852,12 +8852,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -8907,7 +8907,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>10:45 AM</t>
+          <t>11:15 AM</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>9:30 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -9017,7 +9017,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>9:30 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>9:30 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>9:55 AM</t>
+          <t>9:15 AM</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9182,12 +9182,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>10:25 AM</t>
+          <t>9:15 AM</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>10:35 AM</t>
+          <t>9:15 AM</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>10:35 AM</t>
+          <t>9:30 AM</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -9347,12 +9347,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>10:50 AM</t>
+          <t>9:30 AM</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>10:50 AM</t>
+          <t>9:30 AM</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>10:50 AM</t>
+          <t>9:45 AM</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Board 3</t>
+          <t>Board 1</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -9512,12 +9512,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>11:05 AM</t>
+          <t>9:45 AM</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Board 1</t>
+          <t>Board 2</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>11:05 AM</t>
+          <t>9:45 AM</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Board 2</t>
+          <t>Board 3</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -9622,7 +9622,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>11:20 AM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>11:35 AM</t>
+          <t>10:15 AM</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -9877,7 +9877,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>pool_2639-GA-3</t>
+          <t>pool_2639-GB-2</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -9887,17 +9887,17 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>26 to 39 - Group A</t>
+          <t>26 to 39 - Group B</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2639-GA-3</t>
+          <t>2639-GB-2</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>8:30 AM</t>
+          <t>8:20 AM</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -9912,12 +9912,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
+          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tushar", "age": 33}</t>
+          <t>{"type": "fixed", "name": "Sudip Parui", "age": 38}</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -9932,7 +9932,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>pool_2639-GB-2</t>
+          <t>pool_2639-GA-8</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>26 to 39 - Group B</t>
+          <t>26 to 39 - Group A</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2639-GB-2</t>
+          <t>2639-GA-8</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Suraj Kakkar", "age": 29}</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sudip Parui", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Tushar", "age": 33}</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -10007,12 +10007,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>8:50 AM</t>
+          <t>8:40 AM</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -10042,7 +10042,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>pool_2639-GA-4</t>
+          <t>pool_2639-GB-8</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>26 to 39 - Group A</t>
+          <t>26 to 39 - Group B</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2639-GA-4</t>
+          <t>2639-GB-8</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Suraj Kakkar", "age": 29}</t>
+          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tapabrata Dutta", "age": 31}</t>
+          <t>{"type": "fixed", "name": "Sudip Parui", "age": 38}</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10097,7 +10097,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>pool_2639-GB-4</t>
+          <t>pool_40P-GA-1</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10107,22 +10107,22 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>26 to 39 - Group B</t>
+          <t>40 and above - Group A</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2639-GB-4</t>
+          <t>40P-GA-1</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>9:20 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
+          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -10152,7 +10152,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>pool_2639-GA-5</t>
+          <t>pool_2639-GA-4</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2639-GA-5</t>
+          <t>2639-GA-4</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>9:20 AM</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tej", "age": 32}</t>
+          <t>{"type": "fixed", "name": "Suraj Kakkar", "age": 29}</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tushar", "age": 33}</t>
+          <t>{"type": "fixed", "name": "Tapabrata Dutta", "age": 31}</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -10207,7 +10207,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>pool_2639-GB-5</t>
+          <t>pool_2639-GA-5</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10217,17 +10217,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>26 to 39 - Group B</t>
+          <t>26 to 39 - Group A</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2639-GB-5</t>
+          <t>2639-GA-5</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>9:20 AM</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sudip Parui", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Tej", "age": 32}</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Tushar", "age": 33}</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -10282,12 +10282,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -10317,7 +10317,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>pool_2639-GA-7</t>
+          <t>pool_2639-GB-5</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10327,22 +10327,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>26 to 39 - Group A</t>
+          <t>26 to 39 - Group B</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2639-GA-7</t>
+          <t>2639-GB-5</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -10352,12 +10352,12 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tapabrata Dutta", "age": 31}</t>
+          <t>{"type": "fixed", "name": "Sudip Parui", "age": 38}</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tushar", "age": 33}</t>
+          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -10372,7 +10372,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>pool_2639-GB-6</t>
+          <t>pool_2639-GA-7</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10382,22 +10382,22 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>26 to 39 - Group B</t>
+          <t>26 to 39 - Group A</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2639-GB-6</t>
+          <t>2639-GA-7</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>11:20 AM</t>
+          <t>10:50 AM</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Japan Parikh", "age": 37}</t>
+          <t>{"type": "fixed", "name": "Tapabrata Dutta", "age": 31}</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sudip Parui", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Tushar", "age": 33}</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
@@ -10427,7 +10427,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>pool_2639-GA-8</t>
+          <t>pool_40P-GB-1</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10437,22 +10437,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>26 to 39 - Group A</t>
+          <t>40 and above - Group B</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2639-GA-8</t>
+          <t>40P-GB-1</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>11:30 AM</t>
+          <t>10:50 AM</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Suraj Kakkar", "age": 29}</t>
+          <t>{"type": "fixed", "name": "Vinay Sawant", "age": 49}</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tushar", "age": 33}</t>
+          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
@@ -10482,7 +10482,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>pool_2639-GB-7</t>
+          <t>pool_2639-GB-6</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2639-GB-7</t>
+          <t>2639-GB-6</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>3:15 PM</t>
+          <t>11:10 AM</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Sudip Parui", "age": 38}</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10537,7 +10537,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>pool_40P-GA-1</t>
+          <t>pool_40P-GA-3</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -10552,12 +10552,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>40P-GA-1</t>
+          <t>40P-GA-3</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>3:30 PM</t>
+          <t>11:10 AM</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -10572,12 +10572,12 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
+          <t>{"type": "fixed", "name": "Oscar Dsa", "age": 46}</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10592,7 +10592,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>pool_2639-GA-9</t>
+          <t>pool_40P-GA-2</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -10602,17 +10602,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>26 to 39 - Group A</t>
+          <t>40 and above - Group A</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2639-GA-9</t>
+          <t>40P-GA-2</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>3:40 PM</t>
+          <t>11:30 AM</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -10627,12 +10627,12 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
+          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tapabrata Dutta", "age": 31}</t>
+          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10647,7 +10647,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>pool_2639-GB-8</t>
+          <t>pool_40P-GB-6</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -10657,17 +10657,17 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>26 to 39 - Group B</t>
+          <t>40 and above - Group B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2639-GB-8</t>
+          <t>40P-GB-6</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>3:50 PM</t>
+          <t>11:30 AM</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -10682,12 +10682,12 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
+          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sudip Parui", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -10702,7 +10702,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>pool_2639-GA-10</t>
+          <t>pool_2639-GB-4</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -10712,17 +10712,17 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>26 to 39 - Group A</t>
+          <t>26 to 39 - Group B</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2639-GA-10</t>
+          <t>2639-GB-4</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>4:10 PM</t>
+          <t>11:50 AM</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
+          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tej", "age": 32}</t>
+          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -10757,7 +10757,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>pool_2639-GB-9</t>
+          <t>pool_U26-GA-1</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -10767,17 +10767,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>26 to 39 - Group B</t>
+          <t>Under 26 - Group A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2639-GB-9</t>
+          <t>U26-GA-1</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>4:10 PM</t>
+          <t>11:50 AM</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -10792,12 +10792,12 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Sankalp Bhatnagar", "age": 18}</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Rutvij sawant", "age": 20}</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10812,7 +10812,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>pool_40P-GB-1</t>
+          <t>pool_2639-GA-3</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -10822,22 +10822,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>40 and above - Group B</t>
+          <t>26 to 39 - Group A</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>40P-GB-1</t>
+          <t>2639-GA-3</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>4:30 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinay Sawant", "age": 49}</t>
+          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
+          <t>{"type": "fixed", "name": "Tushar", "age": 33}</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10867,7 +10867,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>pool_40P-GA-2</t>
+          <t>pool_40P-GB-3</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -10877,22 +10877,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>40 and above - Group A</t>
+          <t>40 and above - Group B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>40P-GA-2</t>
+          <t>40P-GB-3</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>5:10 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
+          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10922,7 +10922,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>pool_40P-GB-2</t>
+          <t>pool_40P-GA-7</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -10932,22 +10932,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>40 and above - Group B</t>
+          <t>40 and above - Group A</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>40P-GB-2</t>
+          <t>40P-GA-7</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>5:25 PM</t>
+          <t>3:20 PM</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinay Sawant", "age": 49}</t>
+          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
+          <t>{"type": "fixed", "name": "Oscar Dsa", "age": 46}</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -10977,7 +10977,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>pool_40P-GA-3</t>
+          <t>pool_U26-GA-2</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -10987,22 +10987,22 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>40 and above - Group A</t>
+          <t>Under 26 - Group A</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>40P-GA-3</t>
+          <t>U26-GA-2</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>5:30 PM</t>
+          <t>3:20 PM</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -11012,12 +11012,12 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
+          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Oscar Dsa", "age": 46}</t>
+          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11032,7 +11032,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>pool_40P-GB-3</t>
+          <t>pool_2639-GA-9</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11042,22 +11042,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>40 and above - Group B</t>
+          <t>26 to 39 - Group A</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>40P-GB-3</t>
+          <t>2639-GA-9</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>5:55 PM</t>
+          <t>3:40 PM</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -11067,12 +11067,12 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
+          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
+          <t>{"type": "fixed", "name": "Tapabrata Dutta", "age": 31}</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11087,7 +11087,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>pool_40P-GA-4</t>
+          <t>pool_U26-GB-1</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11097,22 +11097,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>40 and above - Group A</t>
+          <t>Under 26 - Group B</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>40P-GA-4</t>
+          <t>U26-GB-1</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>6:00 PM</t>
+          <t>3:40 PM</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
+          <t>{"type": "fixed", "name": "Shravan Gajera", "age": 23}</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Oscar Dsa", "age": 46}</t>
+          <t>{"type": "fixed", "name": "Ishaan Merchant", "age": 25}</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -11142,7 +11142,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>pool_40P-GB-4</t>
+          <t>pool_2639-GB-7</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11152,17 +11152,17 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>40 and above - Group B</t>
+          <t>26 to 39 - Group B</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>40P-GB-4</t>
+          <t>2639-GB-7</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>6:25 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -11177,12 +11177,12 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinay Sawant", "age": 49}</t>
+          <t>{"type": "fixed", "name": "Japan Parikh", "age": 37}</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
+          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
@@ -11197,7 +11197,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>pool_40P-GB-5</t>
+          <t>pool_40P-GA-4</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11207,17 +11207,17 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>40 and above - Group B</t>
+          <t>40 and above - Group A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>40P-GB-5</t>
+          <t>40P-GA-4</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>6:25 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
+          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
+          <t>{"type": "fixed", "name": "Oscar Dsa", "age": 46}</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11252,7 +11252,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>pool_40P-GA-5</t>
+          <t>pool_U26-GA-3</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11262,17 +11262,17 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>40 and above - Group A</t>
+          <t>Under 26 - Group A</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>40P-GA-5</t>
+          <t>U26-GA-3</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>6:45 PM</t>
+          <t>4:20 PM</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
+          <t>{"type": "fixed", "name": "Rutvij sawant", "age": 20}</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -11307,7 +11307,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>pool_40P-GB-6</t>
+          <t>pool_U26-GB-2</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11317,17 +11317,17 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>40 and above - Group B</t>
+          <t>Under 26 - Group B</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>40P-GB-6</t>
+          <t>U26-GB-2</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>6:55 PM</t>
+          <t>4:20 PM</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -11342,12 +11342,12 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
+          <t>{"type": "fixed", "name": "Shravan Gajera", "age": 23}</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
+          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -11362,7 +11362,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>pool_U26-GA-1</t>
+          <t>pool_2639-GB-9</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11372,22 +11372,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Under 26 - Group A</t>
+          <t>26 to 39 - Group B</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>U26-GA-1</t>
+          <t>2639-GB-9</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>7:05 PM</t>
+          <t>4:40 PM</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -11397,12 +11397,12 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sankalp Bhatnagar", "age": 18}</t>
+          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rutvij sawant", "age": 20}</t>
+          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
@@ -11417,7 +11417,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>pool_40P-GA-6</t>
+          <t>pool_40P-GA-5</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11432,17 +11432,17 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>40P-GA-6</t>
+          <t>40P-GA-5</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>7:15 PM</t>
+          <t>4:40 PM</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
+          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -11472,7 +11472,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>pool_2639-GB-10</t>
+          <t>pool_2639-GA-10</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11482,17 +11482,17 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>26 to 39 - Group B</t>
+          <t>26 to 39 - Group A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2639-GB-10</t>
+          <t>2639-GA-10</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>7:35 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
+          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Tej", "age": 32}</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -11527,7 +11527,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>pool_40P-GB-7</t>
+          <t>pool_40P-GA-9</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11537,17 +11537,17 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>40 and above - Group B</t>
+          <t>40 and above - Group A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>40P-GB-7</t>
+          <t>40P-GA-9</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>7:50 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -11562,12 +11562,12 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
+          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
+          <t>{"type": "fixed", "name": "Oscar Dsa", "age": 46}</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -11582,7 +11582,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>pool_40P-GA-7</t>
+          <t>pool_40P-GA-6</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11597,12 +11597,12 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>40P-GA-7</t>
+          <t>40P-GA-6</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>8:10 PM</t>
+          <t>5:20 PM</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -11617,12 +11617,12 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Oscar Dsa", "age": 46}</t>
+          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -11637,7 +11637,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>pool_40P-GB-8</t>
+          <t>pool_40P-GB-2</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -11652,12 +11652,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>40P-GB-8</t>
+          <t>40P-GB-2</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>8:20 PM</t>
+          <t>5:20 PM</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
+          <t>{"type": "fixed", "name": "Vinay Sawant", "age": 49}</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
+          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -11692,7 +11692,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>pool_40P-GA-8</t>
+          <t>pool_40P-GB-7</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -11702,17 +11702,17 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>40 and above - Group A</t>
+          <t>40 and above - Group B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>40P-GA-8</t>
+          <t>40P-GB-7</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>8:40 PM</t>
+          <t>5:40 PM</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -11727,12 +11727,12 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -11747,7 +11747,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>pool_40P-GB-9</t>
+          <t>pool_U26-GB-3</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -11757,17 +11757,17 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>40 and above - Group B</t>
+          <t>Under 26 - Group B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>40P-GB-9</t>
+          <t>U26-GB-3</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>8:40 PM</t>
+          <t>5:40 PM</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -11782,12 +11782,12 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinay Sawant", "age": 49}</t>
+          <t>{"type": "fixed", "name": "Ishaan Merchant", "age": 25}</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
+          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -11802,7 +11802,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>pool_40P-GB-10</t>
+          <t>pool_2639-GB-10</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -11812,17 +11812,17 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>40 and above - Group B</t>
+          <t>26 to 39 - Group B</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>40P-GB-10</t>
+          <t>2639-GB-10</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>9:00 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -11837,12 +11837,12 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
+          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
+          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -11857,7 +11857,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>pool_U26-GB-1</t>
+          <t>pool_40P-GB-10</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -11867,17 +11867,17 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Under 26 - Group B</t>
+          <t>40 and above - Group B</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>U26-GB-1</t>
+          <t>40P-GB-10</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>9:00 PM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -11892,12 +11892,12 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Shravan Gajera", "age": 23}</t>
+          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ishaan Merchant", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -11912,7 +11912,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>pool_40P-GA-9</t>
+          <t>pool_40P-GB-4</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -11922,17 +11922,17 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>40 and above - Group A</t>
+          <t>40 and above - Group B</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>40P-GA-9</t>
+          <t>40P-GB-4</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>9:20 PM</t>
+          <t>6:20 PM</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Vinay Sawant", "age": 49}</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Oscar Dsa", "age": 46}</t>
+          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -11967,7 +11967,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>pool_U26-GA-2</t>
+          <t>pool_U26-GA-4</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>U26-GA-2</t>
+          <t>U26-GA-4</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>9:20 PM</t>
+          <t>6:20 PM</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
+          <t>{"type": "fixed", "name": "Sankalp Bhatnagar", "age": 18}</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -12022,7 +12022,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>pool_U26-GB-2</t>
+          <t>pool_40P-GA-8</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12032,17 +12032,17 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Under 26 - Group B</t>
+          <t>40 and above - Group A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>U26-GB-2</t>
+          <t>40P-GA-8</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>9:40 PM</t>
+          <t>6:40 PM</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Shravan Gajera", "age": 23}</t>
+          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -12077,7 +12077,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>pool_40P-GA-10</t>
+          <t>pool_40P-GB-5</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12087,17 +12087,17 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>40 and above - Group A</t>
+          <t>40 and above - Group B</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>40P-GA-10</t>
+          <t>40P-GB-5</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>9:50 PM</t>
+          <t>6:40 PM</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -12112,12 +12112,12 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
+          <t>{"type": "fixed", "name": "Prasad Akshintala", "age": 56}</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
@@ -12132,7 +12132,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>pool_U26-GA-3</t>
+          <t>pool_U26-GA-5</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12147,27 +12147,27 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>U26-GA-3</t>
+          <t>U26-GA-5</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
+          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12187,7 +12187,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>pool_U26-GB-3</t>
+          <t>pool_U26-GB-4</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12202,32 +12202,32 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>U26-GB-3</t>
+          <t>U26-GB-4</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ishaan Merchant", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -12242,7 +12242,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>pool_U26-GA-4</t>
+          <t>pool_40P-GA-10</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12252,37 +12252,37 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Under 26 - Group A</t>
+          <t>40 and above - Group A</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>U26-GA-4</t>
+          <t>40P-GA-10</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>8:20 AM</t>
+          <t>7:20 PM</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
+          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sankalp Bhatnagar", "age": 18}</t>
+          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -12297,7 +12297,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>pool_U26-GB-4</t>
+          <t>pool_U26-GA-6</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12307,37 +12307,37 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Under 26 - Group B</t>
+          <t>Under 26 - Group A</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>U26-GB-4</t>
+          <t>U26-GA-6</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>8:30 AM</t>
+          <t>7:20 PM</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Sankalp Bhatnagar", "age": 18}</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
@@ -12352,7 +12352,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>pool_U26-GA-5</t>
+          <t>pool_40P-GB-8</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Under 26 - Group A</t>
+          <t>40 and above - Group B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>U26-GA-5</t>
+          <t>40P-GB-8</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>8:50 AM</t>
+          <t>7:40 PM</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -12382,17 +12382,17 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
+          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rutvij sawant", "age": 20}</t>
+          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -12407,7 +12407,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>pool_U26-GB-5</t>
+          <t>pool_40P-GB-9</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12417,17 +12417,17 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Under 26 - Group B</t>
+          <t>40 and above - Group B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>U26-GB-5</t>
+          <t>40P-GB-9</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>7:40 PM</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -12437,17 +12437,17 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ishaan Merchant", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Vinay Sawant", "age": 49}</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
@@ -12462,7 +12462,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>pool_U26-GB-6</t>
+          <t>pool_2639-SF1</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12472,37 +12472,37 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Under 26 - Group B</t>
+          <t>26 to 39 - Semifinal</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>U26-GB-6</t>
+          <t>2639-SF1</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>9:30 AM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Shravan Gajera", "age": 23}</t>
+          <t>{"type": "manual", "name": "Group A 1st"}</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "manual", "name": "Group B 2nd"}</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -12517,7 +12517,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>pool_U26-GA-6</t>
+          <t>pool_U26-GB-5</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12527,37 +12527,37 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Under 26 - Group A</t>
+          <t>Under 26 - Group B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>U26-GA-6</t>
+          <t>U26-GB-5</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>9:50 AM</t>
+          <t>8:00 PM</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
+          <t>{"type": "fixed", "name": "Ishaan Merchant", "age": 25}</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sankalp Bhatnagar", "age": 18}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -12572,7 +12572,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>pool_U26-SF1</t>
+          <t>pool_2639-SF2</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12582,17 +12582,17 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Under 26 - Semifinal</t>
+          <t>26 to 39 - Semifinal</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>U26-SF1</t>
+          <t>2639-SF2</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>10:10 AM</t>
+          <t>8:20 PM</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -12602,17 +12602,17 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 1st"}</t>
+          <t>{"type": "manual", "name": "Group B 1st"}</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 2nd"}</t>
+          <t>{"type": "manual", "name": "Group A 2nd"}</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -12627,7 +12627,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>pool_U26-SF2</t>
+          <t>pool_40P-SF1</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12637,17 +12637,17 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Under 26 - Semifinal</t>
+          <t>40 and above - Semifinal</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>U26-SF2</t>
+          <t>40P-SF1</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>10:10 AM</t>
+          <t>8:20 PM</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -12657,7 +12657,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -12682,7 +12682,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>pool_2639-SF1</t>
+          <t>pool_2639-FINAL</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12692,37 +12692,37 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>26 to 39 - Semifinal</t>
+          <t>26 to 39 - Final</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2639-SF1</t>
+          <t>2639-FINAL</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>8:40 PM</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 1st"}</t>
+          <t>{"type": "placeholder", "ref": "2639-SF1"}</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 2nd"}</t>
+          <t>{"type": "placeholder", "ref": "2639-SF2"}</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -12737,7 +12737,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>pool_2639-SF2</t>
+          <t>pool_U26-GB-6</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12747,37 +12747,37 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>26 to 39 - Semifinal</t>
+          <t>Under 26 - Group B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2639-SF2</t>
+          <t>U26-GB-6</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>8:40 PM</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 1st"}</t>
+          <t>{"type": "fixed", "name": "Shravan Gajera", "age": 23}</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 2nd"}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
@@ -12792,7 +12792,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>pool_2639-FINAL</t>
+          <t>pool_U26-SF1</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12802,17 +12802,17 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>26 to 39 - Final</t>
+          <t>Under 26 - Semifinal</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2639-FINAL</t>
+          <t>U26-SF1</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>10:50 AM</t>
+          <t>9:00 PM</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -12822,17 +12822,17 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "2639-SF1"}</t>
+          <t>{"type": "manual", "name": "Group A 1st"}</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "2639-SF2"}</t>
+          <t>{"type": "manual", "name": "Group B 2nd"}</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
@@ -12847,7 +12847,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>pool_40P-SF1</t>
+          <t>pool_U26-SF2</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12857,17 +12857,17 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>40 and above - Semifinal</t>
+          <t>Under 26 - Semifinal</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>40P-SF1</t>
+          <t>U26-SF2</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>10:50 AM</t>
+          <t>9:00 PM</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -12922,7 +12922,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>11:10 AM</t>
+          <t>9:20 PM</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -12977,7 +12977,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>11:10 AM</t>
+          <t>9:20 PM</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>11:30 AM</t>
+          <t>9:40 PM</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">

--- a/ekta-games-import-297.xlsx
+++ b/ekta-games-import-297.xlsx
@@ -987,7 +987,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>8:45 AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8:15 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8:15 AM</t>
+          <t>9:15 AM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8:30 AM</t>
+          <t>9:15 AM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8:45 AM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8:45 AM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>10:45 AM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>10:45 AM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9:15 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9:15 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>11:15 AM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>11:15 AM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10:45 AM</t>
+          <t>11:30 AM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10:45 AM</t>
+          <t>11:30 AM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>11:45 AM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1792,7 +1792,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tt_men_A46-QF3</t>
+          <t>tt_men_A46-QF2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>A46-QF3</t>
+          <t>A46-QF2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ghansyam nawani", "age": 60}</t>
+          <t>{"type": "fixed", "name": "Vinod Agrawal", "age": 55}</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "HARSHAPRABHAT SHETTY", "age": 62}</t>
+          <t>{"type": "fixed", "name": "Kishore Kumar", "age": 70}</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1847,7 +1847,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tt_men_U36-GB-1</t>
+          <t>tt_men_A46-R1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1857,22 +1857,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Under 36 - Group B</t>
+          <t>Above 46 - Round 1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>U36-GB-1</t>
+          <t>A46-R1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8:30 AM</t>
+          <t>8:00 AM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Prakshal Shah", "age": 32}</t>
+          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amar Parulekar", "age": 32}</t>
+          <t>{"type": "fixed", "name": "Ajit nair", "age": 59}</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1902,7 +1902,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tt_men_U26-2</t>
+          <t>tt_men_A46-QF1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1912,17 +1912,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Under 26 - Pool</t>
+          <t>Above 46 - Quarterfinal</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>U26-2</t>
+          <t>A46-QF1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3:38 PM</t>
+          <t>8:15 AM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
+          <t>{"type": "placeholder", "ref": "A46-R1"}</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
+          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tt_men_U36-GA-2</t>
+          <t>tt_men_A46-QF3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1967,22 +1967,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Under 36 - Group A</t>
+          <t>Above 46 - Quarterfinal</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>U36-GA-2</t>
+          <t>A46-QF3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>8:15 AM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Jashit Bajaj", "age": 28}</t>
+          <t>{"type": "fixed", "name": "Ghansyam nawani", "age": 60}</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tapabrata Dutta", "age": 31}</t>
+          <t>{"type": "fixed", "name": "HARSHAPRABHAT SHETTY", "age": 62}</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2012,7 +2012,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tt_men_U46-GA-9</t>
+          <t>tt_men_A46-QF4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2022,22 +2022,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Under 46 - Group A</t>
+          <t>Above 46 - Quarterfinal</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>U46-GA-9</t>
+          <t>A46-QF4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4:10 PM</t>
+          <t>8:30 AM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sudip Parui", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Anuj Shah", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Sushil Dashpute", "age": 62}</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2067,7 +2067,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tt_men_U15-GA-1</t>
+          <t>tt_men_A46-SF1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2077,22 +2077,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Under 15 - Group A</t>
+          <t>Above 46 - Semifinal</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>U15-GA-1</t>
+          <t>A46-SF1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>8:30 AM</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Shaurya Tripathi", "age": 10}</t>
+          <t>{"type": "placeholder", "ref": "A46-QF1"}</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Parth yadav", "age": 10}</t>
+          <t>{"type": "placeholder", "ref": "A46-QF2"}</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2122,7 +2122,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tt_men_U15-GB-1</t>
+          <t>tt_men_A46-SF2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Under 15 - Group B</t>
+          <t>Above 46 - Semifinal</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>U15-GB-1</t>
+          <t>A46-SF2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>8:45 AM</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2157,12 +2157,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Viaan Neema", "age": 12}</t>
+          <t>{"type": "placeholder", "ref": "A46-QF3"}</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Yash agarwal", "age": 13}</t>
+          <t>{"type": "placeholder", "ref": "A46-QF4"}</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2177,7 +2177,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tt_men_U46-GA-5</t>
+          <t>tt_men_A46-FINAL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2187,17 +2187,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Under 46 - Group A</t>
+          <t>Above 46 - Final</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>U46-GA-5</t>
+          <t>A46-FINAL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5:30 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
+          <t>{"type": "placeholder", "ref": "A46-SF1"}</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sudip Parui", "age": 38}</t>
+          <t>{"type": "placeholder", "ref": "A46-SF2"}</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2232,7 +2232,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tt_men_U46-GA-7</t>
+          <t>tt_men_U36-GB-1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2242,22 +2242,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Under 46 - Group A</t>
+          <t>Under 36 - Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>U46-GA-7</t>
+          <t>U36-GB-1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5:55 PM</t>
+          <t>11:45 AM</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Prakshal Shah", "age": 32}</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Anuj Shah", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Amar Parulekar", "age": 32}</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2287,7 +2287,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tt_men_U36-GA-1</t>
+          <t>tt_men_U26-2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Under 36 - Group A</t>
+          <t>Under 26 - Pool</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>U36-GA-1</t>
+          <t>U26-2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6:11 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Jashit Bajaj", "age": 28}</t>
+          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
+          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tt_men_U36-GA-3</t>
+          <t>tt_men_U36-GA-2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2357,17 +2357,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>U36-GA-3</t>
+          <t>U36-GA-2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6:36 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
+          <t>{"type": "fixed", "name": "Jashit Bajaj", "age": 28}</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2397,7 +2397,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tt_men_A46-QF2</t>
+          <t>tt_men_U15-GA-1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2407,17 +2407,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Above 46 - Quarterfinal</t>
+          <t>Under 15 - Group A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>A46-QF2</t>
+          <t>U15-GA-1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6:40 PM</t>
+          <t>3:15 PM</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinod Agrawal", "age": 55}</t>
+          <t>{"type": "fixed", "name": "Shaurya Tripathi", "age": 10}</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Kishore Kumar", "age": 70}</t>
+          <t>{"type": "fixed", "name": "Parth yadav", "age": 10}</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2452,7 +2452,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tt_men_U15-GB-2</t>
+          <t>tt_men_U46-GA-9</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Under 15 - Group B</t>
+          <t>Under 46 - Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>U15-GB-2</t>
+          <t>U46-GA-9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6:57 PM</t>
+          <t>3:15 PM</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Viaan Neema", "age": 12}</t>
+          <t>{"type": "fixed", "name": "Sudip Parui", "age": 38}</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Hridh jhala", "age": 13}</t>
+          <t>{"type": "fixed", "name": "Anuj Shah", "age": 39}</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2507,7 +2507,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tt_men_U15-GB-3</t>
+          <t>tt_men_U15-GB-1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>U15-GB-3</t>
+          <t>U15-GB-1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7:22 PM</t>
+          <t>3:30 PM</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2542,12 +2542,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
+          <t>{"type": "fixed", "name": "Viaan Neema", "age": 12}</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>{"type": "fixed", "name": "Yash agarwal", "age": 13}</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>{"type": "fixed", "name": "Hridh jhala", "age": 13}</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2562,7 +2562,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tt_men_U46-GB-10</t>
+          <t>tt_men_U46-GB-8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2577,12 +2577,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>U46-GB-10</t>
+          <t>U46-GB-8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7:35 PM</t>
+          <t>3:30 PM</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
+          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2617,7 +2617,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tt_men_U36-GB-2</t>
+          <t>tt_men_U26-8</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Under 36 - Group B</t>
+          <t>Under 26 - Pool</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>U36-GB-2</t>
+          <t>U26-8</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7:50 PM</t>
+          <t>3:45 PM</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Prakshal Shah", "age": 32}</t>
+          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tej", "age": 32}</t>
+          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2672,7 +2672,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tt_men_U46-GA-1</t>
+          <t>tt_men_U46-GA-8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2687,17 +2687,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>U46-GA-1</t>
+          <t>U46-GA-8</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7:55 PM</t>
+          <t>3:45 PM</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
+          <t>{"type": "fixed", "name": "Sudip Parui", "age": 38}</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2727,7 +2727,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tt_men_U46-GB-3</t>
+          <t>tt_men_U15-GB-2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2737,22 +2737,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Under 15 - Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>U46-GB-3</t>
+          <t>U15-GB-2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>8:05 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Viaan Neema", "age": 12}</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Hridh jhala", "age": 13}</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2782,7 +2782,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tt_men_U36-GB-3</t>
+          <t>tt_men_U36-GA-1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2792,22 +2792,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Under 36 - Group B</t>
+          <t>Under 36 - Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>U36-GB-3</t>
+          <t>U36-GA-1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>8:10 PM</t>
+          <t>4:00 PM</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amar Parulekar", "age": 32}</t>
+          <t>{"type": "fixed", "name": "Jashit Bajaj", "age": 28}</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tej", "age": 32}</t>
+          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2837,7 +2837,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tt_men_U46-GA-2</t>
+          <t>tt_men_U36-GB-2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Under 46 - Group A</t>
+          <t>Under 36 - Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>U46-GA-2</t>
+          <t>U36-GB-2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>8:20 PM</t>
+          <t>4:15 PM</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
+          <t>{"type": "fixed", "name": "Prakshal Shah", "age": 32}</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sudip Parui", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Tej", "age": 32}</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2892,7 +2892,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>tt_men_U46-GA-6</t>
+          <t>tt_men_U46-GA-2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>U46-GA-6</t>
+          <t>U46-GA-2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>8:25 PM</t>
+          <t>4:15 PM</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Sudip Parui", "age": 38}</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2947,7 +2947,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tt_men_U46-GB-4</t>
+          <t>tt_men_U15-GB-3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2957,17 +2957,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Under 15 - Group B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>U46-GB-4</t>
+          <t>U15-GB-3</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>8:35 PM</t>
+          <t>4:30 PM</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2982,12 +2982,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Yash agarwal", "age": 13}</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
+          <t>{"type": "fixed", "name": "Hridh jhala", "age": 13}</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3002,7 +3002,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>tt_men_U46-GA-4</t>
+          <t>tt_men_U46-GB-3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3012,17 +3012,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Under 46 - Group A</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>U46-GA-4</t>
+          <t>U46-GB-3</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>8:40 PM</t>
+          <t>4:30 PM</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
+          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Anuj Shah", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3057,7 +3057,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tt_men_U46-GA-8</t>
+          <t>tt_men_U36-GA-3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3067,17 +3067,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Under 46 - Group A</t>
+          <t>Under 36 - Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>U46-GA-8</t>
+          <t>U36-GA-3</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>8:50 PM</t>
+          <t>4:45 PM</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sudip Parui", "age": 38}</t>
+          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Tapabrata Dutta", "age": 31}</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3112,7 +3112,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>tt_men_U36-SF1</t>
+          <t>tt_men_U46-GA-4</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3122,17 +3122,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Under 36 - Semifinal</t>
+          <t>Under 46 - Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>U36-SF1</t>
+          <t>U46-GA-4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>8:55 PM</t>
+          <t>4:45 PM</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 1st"}</t>
+          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 2nd"}</t>
+          <t>{"type": "fixed", "name": "Anuj Shah", "age": 39}</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3167,7 +3167,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>tt_men_U36-SF2</t>
+          <t>tt_men_U46-GA-5</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3177,17 +3177,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Under 36 - Semifinal</t>
+          <t>Under 46 - Group A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>U36-SF2</t>
+          <t>U46-GA-5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>9:05 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 1st"}</t>
+          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 2nd"}</t>
+          <t>{"type": "fixed", "name": "Sudip Parui", "age": 38}</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3222,7 +3222,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>tt_men_U46-GA-3</t>
+          <t>tt_men_U46-GB-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3232,17 +3232,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Under 46 - Group A</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>U46-GA-3</t>
+          <t>U46-GB-10</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>9:10 PM</t>
+          <t>5:00 PM</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3257,12 +3257,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
+          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3277,7 +3277,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>tt_men_A46-QF4</t>
+          <t>tt_men_U15-GA-2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3287,22 +3287,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Above 46 - Quarterfinal</t>
+          <t>Under 15 - Group A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>A46-QF4</t>
+          <t>U15-GA-2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>9:20 PM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mukul Joshi", "age": 51}</t>
+          <t>{"type": "fixed", "name": "Shaurya Tripathi", "age": 10}</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sushil Dashpute", "age": 62}</t>
+          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3332,7 +3332,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>tt_men_U36-FINAL</t>
+          <t>tt_men_U46-GA-3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Under 36 - Final</t>
+          <t>Under 46 - Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>U36-FINAL</t>
+          <t>U46-GA-3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>9:25 PM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U36-SF1"}</t>
+          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U36-SF2"}</t>
+          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3387,7 +3387,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>tt_men_A46-SF2</t>
+          <t>tt_men_U36-GB-3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3397,22 +3397,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Above 46 - Semifinal</t>
+          <t>Under 36 - Group B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>A46-SF2</t>
+          <t>U36-GB-3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>9:35 PM</t>
+          <t>5:30 PM</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-QF3"}</t>
+          <t>{"type": "fixed", "name": "Amar Parulekar", "age": 32}</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-QF4"}</t>
+          <t>{"type": "fixed", "name": "Tej", "age": 32}</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3442,7 +3442,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>tt_men_U46-GA-10</t>
+          <t>tt_men_U46-GA-7</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3457,17 +3457,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>U46-GA-10</t>
+          <t>U46-GA-7</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>9:40 PM</t>
+          <t>5:30 PM</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>tt_men_U46-GB-8</t>
+          <t>tt_men_U36-SF1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3507,37 +3507,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Under 36 - Semifinal</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>U46-GB-8</t>
+          <t>U36-SF1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>5:45 PM</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
+          <t>{"type": "manual", "name": "Group B 1st"}</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
+          <t>{"type": "manual", "name": "Group A 2nd"}</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3552,7 +3552,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>tt_men_U46-GB-9</t>
+          <t>tt_men_U46-GB-4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>U46-GB-9</t>
+          <t>U46-GB-4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>8:25 AM</t>
+          <t>5:45 PM</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3607,7 +3607,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>tt_men_U26-8</t>
+          <t>tt_men_U26-3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3622,27 +3622,27 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>U26-8</t>
+          <t>U26-3</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>8:50 AM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
+          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3662,7 +3662,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>tt_men_U46-GB-2</t>
+          <t>tt_men_U36-SF2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3672,37 +3672,37 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Under 36 - Semifinal</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>U46-GB-2</t>
+          <t>U36-SF2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>8:50 AM</t>
+          <t>6:00 PM</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
+          <t>{"type": "manual", "name": "Group A 1st"}</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
+          <t>{"type": "manual", "name": "Group B 2nd"}</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3717,7 +3717,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>tt_men_U15-GA-2</t>
+          <t>tt_men_U26-5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3727,17 +3727,17 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Under 15 - Group A</t>
+          <t>Under 26 - Pool</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>U15-GA-2</t>
+          <t>U26-5</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>9:10 AM</t>
+          <t>6:15 PM</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3747,17 +3747,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Shaurya Tripathi", "age": 10}</t>
+          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
+          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3772,7 +3772,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>tt_men_U26-3</t>
+          <t>tt_men_U36-FINAL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3782,17 +3782,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Under 26 - Pool</t>
+          <t>Under 36 - Final</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>U26-3</t>
+          <t>U36-FINAL</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>9:20 AM</t>
+          <t>6:15 PM</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3802,17 +3802,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
+          <t>{"type": "placeholder", "ref": "U36-SF1"}</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
+          <t>{"type": "placeholder", "ref": "U36-SF2"}</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>tt_men_U15-GA-3</t>
+          <t>tt_men_U46-GA-1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3837,17 +3837,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Under 15 - Group A</t>
+          <t>Under 46 - Group A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>U15-GA-3</t>
+          <t>U46-GA-1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>9:35 AM</t>
+          <t>6:30 PM</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3857,17 +3857,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Parth yadav", "age": 10}</t>
+          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
+          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3882,7 +3882,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>tt_men_U15-SF1</t>
+          <t>tt_men_U46-GA-10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3892,17 +3892,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Under 15 - Semifinal</t>
+          <t>Under 46 - Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>U15-SF1</t>
+          <t>U46-GA-10</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>9:50 AM</t>
+          <t>6:30 PM</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3912,17 +3912,17 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 1st"}</t>
+          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 2nd"}</t>
+          <t>{"type": "fixed", "name": "Anuj Shah", "age": 39}</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3937,7 +3937,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>tt_men_U26-4</t>
+          <t>tt_men_U15-GA-3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Under 26 - Pool</t>
+          <t>Under 15 - Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>U26-4</t>
+          <t>U15-GA-3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>9:50 AM</t>
+          <t>6:45 PM</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3967,17 +3967,17 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
+          <t>{"type": "fixed", "name": "Parth yadav", "age": 10}</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3992,7 +3992,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>tt_men_U15-SF2</t>
+          <t>tt_men_U26-4</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4002,37 +4002,37 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Under 15 - Semifinal</t>
+          <t>Under 26 - Pool</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>U15-SF2</t>
+          <t>U26-4</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>10:05 AM</t>
+          <t>6:45 PM</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 1st"}</t>
+          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 2nd"}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4047,7 +4047,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>tt_men_U26-6</t>
+          <t>tt_men_U46-GA-6</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4057,37 +4057,37 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Under 26 - Pool</t>
+          <t>Under 46 - Group A</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>U26-6</t>
+          <t>U46-GA-6</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>10:10 AM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
+          <t>{"type": "fixed", "name": "Ankur Mahante", "age": 38}</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4102,7 +4102,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>tt_men_U26-9</t>
+          <t>tt_men_U46-GB-9</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4112,37 +4112,37 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Under 26 - Pool</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>U26-9</t>
+          <t>U46-GB-9</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>10:20 AM</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
+          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4157,7 +4157,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>tt_men_U15-FINAL</t>
+          <t>tt_men_U15-SF1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4167,37 +4167,37 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Under 15 - Final</t>
+          <t>Under 15 - Semifinal</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>U15-FINAL</t>
+          <t>U15-SF1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>10:25 AM</t>
+          <t>7:15 PM</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U15-SF1"}</t>
+          <t>{"type": "manual", "name": "Group B 1st"}</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U15-SF2"}</t>
+          <t>{"type": "manual", "name": "Group A 2nd"}</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4212,7 +4212,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>tt_men_U26-1</t>
+          <t>tt_men_U15-SF2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4222,37 +4222,37 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Under 26 - Pool</t>
+          <t>Under 15 - Semifinal</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>U26-1</t>
+          <t>U15-SF2</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>10:35 AM</t>
+          <t>7:15 PM</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
+          <t>{"type": "manual", "name": "Group A 1st"}</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
+          <t>{"type": "manual", "name": "Group B 2nd"}</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4267,7 +4267,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>tt_men_U26-10</t>
+          <t>tt_men_U15-FINAL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4277,17 +4277,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Under 26 - Pool</t>
+          <t>Under 15 - Final</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>U26-10</t>
+          <t>U15-FINAL</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>10:40 AM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4297,17 +4297,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
+          <t>{"type": "placeholder", "ref": "U15-SF1"}</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "placeholder", "ref": "U15-SF2"}</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4322,7 +4322,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>tt_men_U26-5</t>
+          <t>tt_men_U26-9</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4337,32 +4337,32 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>U26-5</t>
+          <t>U26-9</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>10:55 AM</t>
+          <t>7:30 PM</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
+          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4377,7 +4377,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>tt_men_U46-GB-1</t>
+          <t>tt_men_U26-6</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4387,37 +4387,37 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Under 26 - Pool</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>U46-GB-1</t>
+          <t>U26-6</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>11:05 AM</t>
+          <t>7:45 PM</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
+          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4432,7 +4432,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>tt_men_U26-7</t>
+          <t>tt_men_U46-GB-2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4442,17 +4442,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Under 26 - Pool</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>U26-7</t>
+          <t>U46-GB-2</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>11:20 AM</t>
+          <t>7:45 PM</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4462,17 +4462,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
+          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4487,7 +4487,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>tt_men_U46-GB-6</t>
+          <t>tt_men_U26-1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4497,37 +4497,37 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Under 26 - Pool</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>U46-GB-6</t>
+          <t>U26-1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>11:25 AM</t>
+          <t>8:10 PM</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
+          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4542,7 +4542,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>tt_men_U26-FINAL</t>
+          <t>tt_men_U26-10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4552,37 +4552,37 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Under 26 - Final</t>
+          <t>Under 26 - Pool</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>U26-FINAL</t>
+          <t>U26-10</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>11:35 AM</t>
+          <t>8:20 PM</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Pool 1st"}</t>
+          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Pool 2nd"}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4597,7 +4597,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>tt_men_U46-GB-5</t>
+          <t>tt_men_U46-GB-1</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4612,12 +4612,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>U46-GB-5</t>
+          <t>U46-GB-1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>11:50 AM</t>
+          <t>8:30 PM</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4627,17 +4627,17 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
+          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
           <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>tt_men_A46-R1</t>
+          <t>tt_men_U46-GB-6</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4662,17 +4662,17 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Above 46 - Round 1</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>A46-R1</t>
+          <t>U46-GB-6</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>8:55 PM</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4682,17 +4682,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Adil Khan", "age": 51}</t>
+          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ajit nair", "age": 59}</t>
+          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4707,7 +4707,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>tt_men_U46-GB-7</t>
+          <t>tt_men_U26-7</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4717,17 +4717,17 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Under 26 - Pool</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>U46-GB-7</t>
+          <t>U26-7</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>9:00 PM</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4737,17 +4737,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
+          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4762,7 +4762,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tt_men_A46-QF1</t>
+          <t>tt_men_U26-FINAL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4772,17 +4772,17 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Above 46 - Quarterfinal</t>
+          <t>Under 26 - Final</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>A46-QF1</t>
+          <t>U26-FINAL</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>3:15 PM</t>
+          <t>9:15 PM</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4792,17 +4792,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-R1"}</t>
+          <t>{"type": "manual", "name": "Pool 1st"}</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Sanjay Kumar", "age": 61}</t>
+          <t>{"type": "manual", "name": "Pool 2nd"}</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4817,7 +4817,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>tt_men_U46-SF1</t>
+          <t>tt_men_U46-GB-5</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4827,17 +4827,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Under 46 - Semifinal</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>U46-SF1</t>
+          <t>U46-GB-5</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>3:15 PM</t>
+          <t>9:15 PM</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4847,17 +4847,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 1st"}</t>
+          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 2nd"}</t>
+          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4872,7 +4872,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>tt_men_A46-SF1</t>
+          <t>tt_men_U46-GB-7</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Above 46 - Semifinal</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>A46-SF1</t>
+          <t>U46-GB-7</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>3:30 PM</t>
+          <t>9:40 PM</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4902,17 +4902,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-QF1"}</t>
+          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-QF2"}</t>
+          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>tt_men_U46-SF2</t>
+          <t>tt_men_U46-SF1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4942,32 +4942,32 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>U46-SF2</t>
+          <t>U46-SF1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>3:30 PM</t>
+          <t>9:55 PM</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 1st"}</t>
+          <t>{"type": "manual", "name": "Group B 1st"}</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 2nd"}</t>
+          <t>{"type": "manual", "name": "Group A 2nd"}</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4982,7 +4982,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>tt_men_A46-FINAL</t>
+          <t>tt_men_U46-SF2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4992,37 +4992,37 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Above 46 - Final</t>
+          <t>Under 46 - Semifinal</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>A46-FINAL</t>
+          <t>U46-SF2</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>3:45 PM</t>
+          <t>9:55 PM</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Aug 16</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-SF1"}</t>
+          <t>{"type": "manual", "name": "Group A 1st"}</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-SF2"}</t>
+          <t>{"type": "manual", "name": "Group B 2nd"}</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>3:45 PM</t>
+          <t>8:00 AM</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5092,7 +5092,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>tt_doubles_QF3</t>
+          <t>tt_doubles_QF2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5107,17 +5107,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>QF3</t>
+          <t>QF2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>9:05 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mayank Aggarwal &amp; Sudip Parui", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Nilesh Bagaria &amp; Parthiv", "age": 44}</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nidhi Sharma &amp; Tushar", "age": 31}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg &amp; Nilesh Mhatre", "age": 25}</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5147,7 +5147,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>tt_doubles_QF2</t>
+          <t>tt_doubles_QF3</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5162,12 +5162,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>QF2</t>
+          <t>QF3</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>10:50 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nilesh Bagaria &amp; Parthiv", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Mayank Aggarwal &amp; Sudip Parui", "age": 39}</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg &amp; Nilesh Mhatre", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Nidhi Sharma &amp; Tushar", "age": 31}</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5202,7 +5202,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>tt_doubles_QF4</t>
+          <t>tt_doubles_QF1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5217,17 +5217,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>QF4</t>
+          <t>QF1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>11:10 AM</t>
+          <t>9:15 AM</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Adil Khan &amp; Anuj Shah", "age": 45}</t>
+          <t>{"type": "fixed", "name": "Tanmay Sharma &amp; Sankalp", "age": 39}</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinit Padia &amp; Pratik Haldiya", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Ravi Modi &amp; Dr Rahul Modi", "age": 32}</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5257,7 +5257,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>tt_doubles_QF1</t>
+          <t>tt_doubles_QF4</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5272,17 +5272,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>QF1</t>
+          <t>QF4</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>11:40 AM</t>
+          <t>9:30 AM</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tanmay Sharma &amp; Sankalp", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Adil Khan &amp; Anuj Shah", "age": 45}</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ravi Modi &amp; Dr Rahul Modi", "age": 32}</t>
+          <t>{"type": "fixed", "name": "Vinit Padia &amp; Pratik Haldiya", "age": 44}</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>11:55 AM</t>
+          <t>9:45 AM</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5387,12 +5387,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>4:00 PM</t>
+          <t>9:45 AM</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>4:15 PM</t>
+          <t>10:00 AM</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">

--- a/ekta-games-import-297.xlsx
+++ b/ekta-games-import-297.xlsx
@@ -1047,7 +1047,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9:15 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2177,7 +2177,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tt_men_A46-FINAL</t>
+          <t>tt_men_U36-GB-1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2187,22 +2187,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Above 46 - Final</t>
+          <t>Under 36 - Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A46-FINAL</t>
+          <t>U36-GB-1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>9:15 AM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-SF1"}</t>
+          <t>{"type": "fixed", "name": "Prakshal Shah", "age": 32}</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "A46-SF2"}</t>
+          <t>{"type": "fixed", "name": "Amar Parulekar", "age": 32}</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2232,7 +2232,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tt_men_U36-GB-1</t>
+          <t>tt_men_U36-GA-2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Under 36 - Group B</t>
+          <t>Under 36 - Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>U36-GB-1</t>
+          <t>U36-GA-2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Prakshal Shah", "age": 32}</t>
+          <t>{"type": "fixed", "name": "Jashit Bajaj", "age": 28}</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amar Parulekar", "age": 32}</t>
+          <t>{"type": "fixed", "name": "Tapabrata Dutta", "age": 31}</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2287,7 +2287,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tt_men_U26-2</t>
+          <t>tt_men_U15-GA-1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2297,12 +2297,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Under 26 - Pool</t>
+          <t>Under 15 - Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>U26-2</t>
+          <t>U15-GA-1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
+          <t>{"type": "fixed", "name": "Shaurya Tripathi", "age": 10}</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
+          <t>{"type": "fixed", "name": "Parth yadav", "age": 10}</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tt_men_U36-GA-2</t>
+          <t>tt_men_U26-2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Under 36 - Group A</t>
+          <t>Under 26 - Pool</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>U36-GA-2</t>
+          <t>U26-2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Jashit Bajaj", "age": 28}</t>
+          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tapabrata Dutta", "age": 31}</t>
+          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2397,7 +2397,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tt_men_U15-GA-1</t>
+          <t>tt_men_U15-GB-1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Under 15 - Group A</t>
+          <t>Under 15 - Group B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>U15-GA-1</t>
+          <t>U15-GB-1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Shaurya Tripathi", "age": 10}</t>
+          <t>{"type": "fixed", "name": "Viaan Neema", "age": 12}</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Parth yadav", "age": 10}</t>
+          <t>{"type": "fixed", "name": "Yash agarwal", "age": 13}</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2507,7 +2507,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tt_men_U15-GB-1</t>
+          <t>tt_men_U26-3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Under 15 - Group B</t>
+          <t>Under 26 - Pool</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>U15-GB-1</t>
+          <t>U26-3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2542,12 +2542,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Viaan Neema", "age": 12}</t>
+          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Yash agarwal", "age": 13}</t>
+          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2617,7 +2617,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>tt_men_U26-8</t>
+          <t>tt_men_U15-GB-2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Under 26 - Pool</t>
+          <t>Under 15 - Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>U26-8</t>
+          <t>U15-GB-2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
+          <t>{"type": "fixed", "name": "Viaan Neema", "age": 12}</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Hridh jhala", "age": 13}</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2727,7 +2727,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tt_men_U15-GB-2</t>
+          <t>tt_men_U36-GA-1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Under 15 - Group B</t>
+          <t>Under 36 - Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>U15-GB-2</t>
+          <t>U36-GA-1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Viaan Neema", "age": 12}</t>
+          <t>{"type": "fixed", "name": "Jashit Bajaj", "age": 28}</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Hridh jhala", "age": 13}</t>
+          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2782,7 +2782,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tt_men_U36-GA-1</t>
+          <t>tt_men_U36-GB-2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Under 36 - Group A</t>
+          <t>Under 36 - Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>U36-GA-1</t>
+          <t>U36-GB-2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Jashit Bajaj", "age": 28}</t>
+          <t>{"type": "fixed", "name": "Prakshal Shah", "age": 32}</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
+          <t>{"type": "fixed", "name": "Tej", "age": 32}</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2837,7 +2837,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tt_men_U36-GB-2</t>
+          <t>tt_men_U15-GB-3</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Under 36 - Group B</t>
+          <t>Under 15 - Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>U36-GB-2</t>
+          <t>U15-GB-3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Prakshal Shah", "age": 32}</t>
+          <t>{"type": "fixed", "name": "Yash agarwal", "age": 13}</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tej", "age": 32}</t>
+          <t>{"type": "fixed", "name": "Hridh jhala", "age": 13}</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2947,7 +2947,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tt_men_U15-GB-3</t>
+          <t>tt_men_U15-GA-2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Under 15 - Group B</t>
+          <t>Under 15 - Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>U15-GB-3</t>
+          <t>U15-GA-2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2982,12 +2982,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Yash agarwal", "age": 13}</t>
+          <t>{"type": "fixed", "name": "Shaurya Tripathi", "age": 10}</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Hridh jhala", "age": 13}</t>
+          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3277,7 +3277,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>tt_men_U15-GA-2</t>
+          <t>tt_men_U26-8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Under 15 - Group A</t>
+          <t>Under 26 - Pool</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>U15-GA-2</t>
+          <t>U26-8</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Shaurya Tripathi", "age": 10}</t>
+          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
+          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3607,7 +3607,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>tt_men_U26-3</t>
+          <t>tt_men_U15-GA-3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Under 26 - Pool</t>
+          <t>Under 15 - Group A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>U26-3</t>
+          <t>U15-GA-3</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
+          <t>{"type": "fixed", "name": "Parth yadav", "age": 10}</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3717,7 +3717,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>tt_men_U26-5</t>
+          <t>tt_men_U15-SF1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Under 26 - Pool</t>
+          <t>Under 15 - Semifinal</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>U26-5</t>
+          <t>U15-SF1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
+          <t>{"type": "manual", "name": "Group B 1st"}</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
+          <t>{"type": "manual", "name": "Group A 2nd"}</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3772,7 +3772,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>tt_men_U36-FINAL</t>
+          <t>tt_men_U15-SF2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Under 36 - Final</t>
+          <t>Under 15 - Semifinal</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>U36-FINAL</t>
+          <t>U15-SF2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U36-SF1"}</t>
+          <t>{"type": "manual", "name": "Group A 1st"}</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U36-SF2"}</t>
+          <t>{"type": "manual", "name": "Group B 2nd"}</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3937,7 +3937,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>tt_men_U15-GA-3</t>
+          <t>tt_men_U26-4</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Under 15 - Group A</t>
+          <t>Under 26 - Pool</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>U15-GA-3</t>
+          <t>U26-4</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Parth yadav", "age": 10}</t>
+          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aadit Joshi", "age": 12}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3992,7 +3992,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>tt_men_U26-4</t>
+          <t>tt_men_U26-6</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>U26-4</t>
+          <t>U26-6</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4027,12 +4027,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
+          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4157,7 +4157,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>tt_men_U15-SF1</t>
+          <t>tt_men_U26-9</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4167,17 +4167,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Under 15 - Semifinal</t>
+          <t>Under 26 - Pool</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>U15-SF1</t>
+          <t>U26-9</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>7:15 PM</t>
+          <t>7:20 PM</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 1st"}</t>
+          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 2nd"}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4212,7 +4212,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>tt_men_U15-SF2</t>
+          <t>tt_men_U26-1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4222,17 +4222,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Under 15 - Semifinal</t>
+          <t>Under 26 - Pool</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>U15-SF2</t>
+          <t>U26-1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>7:15 PM</t>
+          <t>7:40 PM</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4247,12 +4247,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 1st"}</t>
+          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 2nd"}</t>
+          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4267,7 +4267,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>tt_men_U15-FINAL</t>
+          <t>tt_men_U46-GB-2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4277,22 +4277,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Under 15 - Final</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>U15-FINAL</t>
+          <t>U46-GB-2</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:40 PM</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4302,12 +4302,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U15-SF1"}</t>
+          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U15-SF2"}</t>
+          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4322,7 +4322,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>tt_men_U26-9</t>
+          <t>tt_men_U46-GB-6</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4332,17 +4332,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Under 26 - Pool</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>U26-9</t>
+          <t>U46-GB-6</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>7:30 PM</t>
+          <t>7:55 PM</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
+          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4377,7 +4377,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>tt_men_U26-6</t>
+          <t>tt_men_U26-5</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>U26-6</t>
+          <t>U26-5</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>7:45 PM</t>
+          <t>8:05 PM</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4432,7 +4432,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>tt_men_U46-GB-2</t>
+          <t>tt_men_U26-10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4442,17 +4442,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Under 26 - Pool</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>U46-GB-2</t>
+          <t>U26-10</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>7:45 PM</t>
+          <t>8:20 PM</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4487,7 +4487,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>tt_men_U26-1</t>
+          <t>tt_men_U46-GB-1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4497,22 +4497,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Under 26 - Pool</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>U26-1</t>
+          <t>U46-GB-1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>8:10 PM</t>
+          <t>8:30 PM</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
+          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
+          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4542,7 +4542,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>tt_men_U26-10</t>
+          <t>tt_men_U46-GB-5</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4552,22 +4552,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Under 26 - Pool</t>
+          <t>Under 46 - Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>U26-10</t>
+          <t>U46-GB-5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>8:20 PM</t>
+          <t>8:55 PM</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Pranit Shriyan", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4597,7 +4597,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>tt_men_U46-GB-1</t>
+          <t>tt_men_U26-7</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4607,22 +4607,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Under 26 - Pool</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>U46-GB-1</t>
+          <t>U26-7</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>8:30 PM</t>
+          <t>9:00 PM</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4632,12 +4632,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nikunj Jhala", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
+          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4652,7 +4652,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>tt_men_U46-GB-6</t>
+          <t>tt_men_U46-GB-7</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4667,17 +4667,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>U46-GB-6</t>
+          <t>U46-GB-7</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>8:55 PM</t>
+          <t>9:15 PM</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Nilesh Bagaria", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4707,7 +4707,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>tt_men_U26-7</t>
+          <t>tt_men_U46-SF1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4717,22 +4717,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Under 26 - Pool</t>
+          <t>Under 46 - Semifinal</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>U26-7</t>
+          <t>U46-SF1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>9:00 PM</t>
+          <t>9:30 PM</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Aaditya Kumar", "age": 17}</t>
+          <t>{"type": "manual", "name": "Group B 1st"}</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Rahul Garg", "age": 25}</t>
+          <t>{"type": "manual", "name": "Group A 2nd"}</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4762,7 +4762,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tt_men_U26-FINAL</t>
+          <t>tt_men_U46-SF2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4772,22 +4772,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Under 26 - Final</t>
+          <t>Under 46 - Semifinal</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>U26-FINAL</t>
+          <t>U46-SF2</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>9:15 PM</t>
+          <t>9:30 PM</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Pool 1st"}</t>
+          <t>{"type": "manual", "name": "Group A 1st"}</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Pool 2nd"}</t>
+          <t>{"type": "manual", "name": "Group B 2nd"}</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4817,7 +4817,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>tt_men_U46-GB-5</t>
+          <t>tt_men_A46-FINAL</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4827,37 +4827,37 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Above 46 - Final</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>U46-GB-5</t>
+          <t>A46-FINAL</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>9:15 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
+          <t>{"type": "placeholder", "ref": "A46-SF1"}</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
+          <t>{"type": "placeholder", "ref": "A46-SF2"}</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4872,7 +4872,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>tt_men_U46-GB-7</t>
+          <t>tt_men_U36-FINAL</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4882,37 +4882,37 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Under 46 - Group B</t>
+          <t>Under 36 - Final</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>U46-GB-7</t>
+          <t>U36-FINAL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>9:40 PM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Piyush Makharia", "age": 43}</t>
+          <t>{"type": "placeholder", "ref": "U36-SF1"}</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Amit Ranka", "age": 45}</t>
+          <t>{"type": "placeholder", "ref": "U36-SF2"}</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4927,7 +4927,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>tt_men_U46-SF1</t>
+          <t>tt_men_U15-FINAL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4937,17 +4937,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Under 46 - Semifinal</t>
+          <t>Under 15 - Final</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>U46-SF1</t>
+          <t>U15-FINAL</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>9:55 PM</t>
+          <t>11:15 AM</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4957,17 +4957,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 1st"}</t>
+          <t>{"type": "placeholder", "ref": "U15-SF1"}</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 2nd"}</t>
+          <t>{"type": "placeholder", "ref": "U15-SF2"}</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4982,7 +4982,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>tt_men_U46-SF2</t>
+          <t>tt_men_U26-FINAL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4992,17 +4992,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Under 46 - Semifinal</t>
+          <t>Under 26 - Final</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>U46-SF2</t>
+          <t>U26-FINAL</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>9:55 PM</t>
+          <t>11:15 AM</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5012,17 +5012,17 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Aug 15</t>
+          <t>Aug 16</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 1st"}</t>
+          <t>{"type": "manual", "name": "Pool 1st"}</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 2nd"}</t>
+          <t>{"type": "manual", "name": "Pool 2nd"}</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>11:30 AM</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>11:30 AM</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">

--- a/ekta-games-import-297.xlsx
+++ b/ekta-games-import-297.xlsx
@@ -16607,7 +16607,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>10:48 AM</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -16642,7 +16642,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>squash_GA-2</t>
+          <t>squash_U15-SF1</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -16652,17 +16652,17 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Above 25 Bracket - Group A</t>
+          <t>U15-SF</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>GA-2</t>
+          <t>U15-SF1</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>11:28 AM</t>
+          <t>11:06 AM</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -16677,12 +16677,12 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
+          <t>{"type": "placeholder", "ref": "U15-R1-M2"}</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
+          <t>{"type": "fixed", "name": "Hridh jhala", "age": 13}</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
@@ -16697,7 +16697,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>squash_GC-3</t>
+          <t>squash_GA-2</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -16707,17 +16707,17 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>15-25 Bracket - Pool</t>
+          <t>Above 25 Bracket - Group A</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>GC-3</t>
+          <t>GA-2</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>3:20 PM</t>
+          <t>11:24 AM</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -16732,12 +16732,12 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
+          <t>{"type": "fixed", "name": "Dr Rahul Modi", "age": 36}</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Shravan Gajera", "age": 23}</t>
+          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -16752,7 +16752,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>squash_GA-3</t>
+          <t>squash_U15-SF2</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -16762,17 +16762,17 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Above 25 Bracket - Group A</t>
+          <t>U15-SF</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>GA-3</t>
+          <t>U15-SF2</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>5:35 PM</t>
+          <t>11:42 AM</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -16787,12 +16787,12 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
+          <t>{"type": "placeholder", "ref": "U15-R1-M1"}</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
+          <t>{"type": "placeholder", "ref": "U15-R1-M3"}</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -16807,7 +16807,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>squash_GB-2</t>
+          <t>squash_GA-3</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -16817,17 +16817,17 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Above 25 Bracket - Group B</t>
+          <t>Above 25 Bracket - Group A</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>GB-2</t>
+          <t>GA-3</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>5:53 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -16842,12 +16842,12 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
+          <t>{"type": "fixed", "name": "Tanmay Sharma", "age": 39}</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Mayank Aggarwal", "age": 40}</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -16862,7 +16862,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>squash_GB-3</t>
+          <t>squash_GC-3</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -16872,17 +16872,17 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Above 25 Bracket - Group B</t>
+          <t>15-25 Bracket - Pool</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>GB-3</t>
+          <t>GC-3</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>6:21 PM</t>
+          <t>3:18 PM</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tejas doshi", "age": 40}</t>
+          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
+          <t>{"type": "fixed", "name": "Shravan Gajera", "age": 23}</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -16917,7 +16917,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>squash_U15-SF1</t>
+          <t>squash_GB-3</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -16927,17 +16927,17 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>U15-SF</t>
+          <t>Above 25 Bracket - Group B</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>U15-SF1</t>
+          <t>GB-3</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>6:39 PM</t>
+          <t>4:20 PM</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -16952,12 +16952,12 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U15-R1-M2"}</t>
+          <t>{"type": "fixed", "name": "Tejas doshi", "age": 40}</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Hridh jhala", "age": 13}</t>
+          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -16972,7 +16972,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>squash_U15-SF2</t>
+          <t>squash_GB-2</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -16982,17 +16982,17 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>U15-SF</t>
+          <t>Above 25 Bracket - Group B</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>U15-SF2</t>
+          <t>GB-2</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>6:57 PM</t>
+          <t>5:30 PM</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -17007,12 +17007,12 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U15-R1-M1"}</t>
+          <t>{"type": "fixed", "name": "Ravi Modi", "age": 29}</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U15-R1-M3"}</t>
+          <t>{"type": "fixed", "name": "Vinit Padia", "age": 44}</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -17027,7 +17027,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>squash_U15-FINAL</t>
+          <t>squash_A25-SF1</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -17037,17 +17037,17 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>U15-F</t>
+          <t>Above 25 Bracket - Semifinal</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>U15-FINAL</t>
+          <t>A25-SF1</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>7:15 PM</t>
+          <t>5:48 PM</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -17062,12 +17062,12 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U15-SF1"}</t>
+          <t>{"type": "manual", "name": "Group A 1st"}</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>{"type": "placeholder", "ref": "U15-SF2"}</t>
+          <t>{"type": "manual", "name": "Group B 2nd"}</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -17082,7 +17082,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>squash_GC-FINAL</t>
+          <t>squash_A25-SF2</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -17092,17 +17092,17 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>15-25 Bracket - Final</t>
+          <t>Above 25 Bracket - Semifinal</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>GC-FINAL</t>
+          <t>A25-SF2</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>7:33 PM</t>
+          <t>6:06 PM</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -17117,12 +17117,12 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Pool 1st"}</t>
+          <t>{"type": "manual", "name": "Group B 1st"}</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Pool 2nd"}</t>
+          <t>{"type": "manual", "name": "Group A 2nd"}</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -17137,7 +17137,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>squash_A25-SF1</t>
+          <t>squash_U15-FINAL</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -17147,17 +17147,17 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Above 25 Bracket - Semifinal</t>
+          <t>U15-F</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>A25-SF1</t>
+          <t>U15-FINAL</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>3:20 PM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -17172,12 +17172,12 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 1st"}</t>
+          <t>{"type": "placeholder", "ref": "U15-SF1"}</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 2nd"}</t>
+          <t>{"type": "placeholder", "ref": "U15-SF2"}</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -17192,7 +17192,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>squash_A25-SF2</t>
+          <t>squash_GC-FINAL</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -17202,17 +17202,17 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Above 25 Bracket - Semifinal</t>
+          <t>15-25 Bracket - Final</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>A25-SF2</t>
+          <t>GC-FINAL</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>3:38 PM</t>
+          <t>3:18 PM</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -17227,12 +17227,12 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group B 1st"}</t>
+          <t>{"type": "manual", "name": "Pool 1st"}</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>{"type": "manual", "name": "Group A 2nd"}</t>
+          <t>{"type": "manual", "name": "Pool 2nd"}</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -17267,7 +17267,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>3:56 PM</t>
+          <t>3:36 PM</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">

--- a/ekta-games-import-297.xlsx
+++ b/ekta-games-import-297.xlsx
@@ -987,12 +987,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8:45 AM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>10:30 AM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>10:45 AM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1152,12 +1152,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9:15 AM</t>
+          <t>10:45 AM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10:30 AM</t>
+          <t>11:00 AM</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10:45 AM</t>
+          <t>11:15 AM</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10:45 AM</t>
+          <t>11:15 AM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>11:30 AM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11:00 AM</t>
+          <t>11:30 AM</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11:15 AM</t>
+          <t>11:45 AM</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11:15 AM</t>
+          <t>11:45 AM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11:30 AM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11:30 AM</t>
+          <t>3:00 PM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11:45 AM</t>
+          <t>3:15 PM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9:15 AM</t>
+          <t>8:45 AM</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2232,7 +2232,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tt_men_U36-GA-2</t>
+          <t>tt_men_U15-GA-1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Under 36 - Group A</t>
+          <t>Under 15 - Group A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>U36-GA-2</t>
+          <t>U15-GA-1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11:45 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Jashit Bajaj", "age": 28}</t>
+          <t>{"type": "fixed", "name": "Shaurya Tripathi", "age": 10}</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Tapabrata Dutta", "age": 31}</t>
+          <t>{"type": "fixed", "name": "Parth yadav", "age": 10}</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2287,7 +2287,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>tt_men_U15-GA-1</t>
+          <t>tt_men_U36-GA-2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2297,22 +2297,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Under 15 - Group A</t>
+          <t>Under 36 - Group A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>U15-GA-1</t>
+          <t>U36-GA-2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Shaurya Tripathi", "age": 10}</t>
+          <t>{"type": "fixed", "name": "Jashit Bajaj", "age": 28}</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Parth yadav", "age": 10}</t>
+          <t>{"type": "fixed", "name": "Tapabrata Dutta", "age": 31}</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2342,7 +2342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>tt_men_U26-2</t>
+          <t>tt_men_U15-GB-1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2352,22 +2352,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Under 26 - Pool</t>
+          <t>Under 15 - Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>U26-2</t>
+          <t>U15-GB-1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3:00 PM</t>
+          <t>9:15 AM</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
+          <t>{"type": "fixed", "name": "Viaan Neema", "age": 12}</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
+          <t>{"type": "fixed", "name": "Yash agarwal", "age": 13}</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2397,7 +2397,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>tt_men_U15-GB-1</t>
+          <t>tt_men_U26-2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2407,22 +2407,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Under 15 - Group B</t>
+          <t>Under 26 - Pool</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>U15-GB-1</t>
+          <t>U26-2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3:15 PM</t>
+          <t>9:15 AM</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2432,12 +2432,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Viaan Neema", "age": 12}</t>
+          <t>{"type": "fixed", "name": "Yuvraj jain", "age": 16}</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{"type": "fixed", "name": "Yash agarwal", "age": 13}</t>
+          <t>{"type": "fixed", "name": "Hryday Goyal", "age": 20}</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
